--- a/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改版履歴" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グループ詳細" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コンポーネント仕様" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="インターフェース定義" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面仕様" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業務フロー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対象オブジェクト" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理概要" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連コンポーネント" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="影響範囲" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1516,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AE14"/>
+  <dimension ref="B1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1557,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>詳細設計書 — グループ詳細</t>
+          <t>詳細設計書 — 概要</t>
         </is>
       </c>
     </row>
@@ -1563,14 +1565,14 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>プロジェクト名</t>
+          <t>機能名</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
@@ -1579,46 +1581,34 @@
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>グループID</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
-      <c r="T3" s="4" t="n"/>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>作成者</t>
-        </is>
-      </c>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="3" t="n"/>
       <c r="Z3" s="3" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="5" t="inlineStr"/>
-      <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>版数</t>
-        </is>
-      </c>
-      <c r="AE3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="48" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>グループ名</t>
+          <t>機能概要</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
@@ -1635,31 +1625,91 @@
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>作成日</t>
-        </is>
-      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
-      <c r="AA4" s="4" t="n"/>
-      <c r="AB4" s="5" t="inlineStr"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
       <c r="AC4" s="3" t="n"/>
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="4" t="n"/>
     </row>
-    <row r="5" ht="10" customHeight="1"/>
-    <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>■ 1. 処理目的</t>
+          <t>目的</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>利用者/利用部門</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AE6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>処理目的</t>
+          <t>起点画面</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -1692,156 +1742,57 @@
       <c r="AD7" s="3" t="n"/>
       <c r="AE7" s="4" t="n"/>
     </row>
-    <row r="8" ht="10" customHeight="1"/>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>■ 2. データ連携概要</t>
+          <t>操作トリガー</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>概要</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
-      <c r="AC10" s="3" t="n"/>
-      <c r="AD10" s="3" t="n"/>
-      <c r="AE10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="10" customHeight="1"/>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>■ 3. 前提条件・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" s="3" t="n"/>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="3" t="n"/>
-      <c r="Z13" s="3" t="n"/>
-      <c r="AA13" s="3" t="n"/>
-      <c r="AB13" s="3" t="n"/>
-      <c r="AC13" s="3" t="n"/>
-      <c r="AD13" s="3" t="n"/>
-      <c r="AE13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
-      <c r="Y14" s="3" t="n"/>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
-      <c r="AC14" s="3" t="n"/>
-      <c r="AD14" s="3" t="n"/>
-      <c r="AE14" s="4" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" s="3" t="n"/>
+      <c r="X8" s="3" t="n"/>
+      <c r="Y8" s="3" t="n"/>
+      <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AE8" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="13">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B1:AE1"/>
+    <mergeCell ref="G7:AE7"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B12:AE12"/>
-    <mergeCell ref="G14:AE14"/>
-    <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="AD3"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="F4:X4"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B9:AE9"/>
-    <mergeCell ref="B6:AE6"/>
-    <mergeCell ref="AE3"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="AB4:AE4"/>
-    <mergeCell ref="Y4:AA4"/>
-    <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="G7:AE7"/>
-    <mergeCell ref="G10:AE10"/>
-    <mergeCell ref="G13:AE13"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G5:AE5"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="G6:AE6"/>
+    <mergeCell ref="G3:AE3"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="G8:AE8"/>
+    <mergeCell ref="G4:AE4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1853,7 +1804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AE19"/>
+  <dimension ref="B1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1892,42 +1843,71 @@
     <row r="1" ht="36" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>詳細設計書 — コンポーネント仕様</t>
+          <t>詳細設計書 — 業務フロー</t>
         </is>
       </c>
     </row>
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="26" customHeight="1">
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>■ コンポーネント仕様</t>
+          <t>No</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>コンポーネント名</t>
+          <t>アクター</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="4" t="n"/>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>分岐条件</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="3" t="n"/>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="3" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>担当処理</t>
-        </is>
-      </c>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
@@ -1935,43 +1915,31 @@
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
-      <c r="T4" s="4" t="n"/>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>入力</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="6" t="inlineStr">
-        <is>
-          <t>出力</t>
-        </is>
-      </c>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="n"/>
-      <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="6" t="inlineStr">
-        <is>
-          <t>エラー処理</t>
-        </is>
-      </c>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="4" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="3" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
@@ -1979,31 +1947,31 @@
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="3" t="n"/>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="5" t="inlineStr"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="5" t="inlineStr"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
       <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="4" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="3" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
@@ -2011,31 +1979,31 @@
       <c r="Q6" s="3" t="n"/>
       <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
-      <c r="T6" s="4" t="n"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
       <c r="Z6" s="3" t="n"/>
       <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
       <c r="AD6" s="3" t="n"/>
       <c r="AE6" s="4" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="3" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="n"/>
@@ -2043,31 +2011,31 @@
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
-      <c r="T7" s="4" t="n"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="5" t="inlineStr"/>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="4" t="n"/>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="3" t="n"/>
+      <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="5" t="inlineStr"/>
+      <c r="AB7" s="3" t="n"/>
+      <c r="AC7" s="3" t="n"/>
       <c r="AD7" s="3" t="n"/>
       <c r="AE7" s="4" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="3" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n"/>
@@ -2075,31 +2043,31 @@
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
-      <c r="T8" s="4" t="n"/>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="5" t="inlineStr"/>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="3" t="n"/>
+      <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="n"/>
-      <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="5" t="inlineStr"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="n"/>
       <c r="AD8" s="3" t="n"/>
       <c r="AE8" s="4" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="3" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n"/>
@@ -2107,31 +2075,31 @@
       <c r="Q9" s="3" t="n"/>
       <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
-      <c r="T9" s="4" t="n"/>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="5" t="inlineStr"/>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="4" t="n"/>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="5" t="inlineStr"/>
+      <c r="AB9" s="3" t="n"/>
+      <c r="AC9" s="3" t="n"/>
       <c r="AD9" s="3" t="n"/>
       <c r="AE9" s="4" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="3" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n"/>
@@ -2139,31 +2107,31 @@
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
-      <c r="T10" s="4" t="n"/>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="4" t="n"/>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="3" t="n"/>
+      <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="4" t="n"/>
-      <c r="AC10" s="5" t="inlineStr"/>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" s="3" t="n"/>
       <c r="AD10" s="3" t="n"/>
       <c r="AE10" s="4" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="3" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="n"/>
@@ -2171,31 +2139,31 @@
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
-      <c r="T11" s="4" t="n"/>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="5" t="inlineStr"/>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="4" t="n"/>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="n"/>
-      <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="5" t="inlineStr"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="n"/>
       <c r="AD11" s="3" t="n"/>
       <c r="AE11" s="4" t="n"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="3" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="n"/>
@@ -2203,31 +2171,31 @@
       <c r="Q12" s="3" t="n"/>
       <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
-      <c r="T12" s="4" t="n"/>
-      <c r="U12" s="5" t="inlineStr"/>
-      <c r="V12" s="3" t="n"/>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="5" t="inlineStr"/>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="4" t="n"/>
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="3" t="n"/>
+      <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="n"/>
-      <c r="AB12" s="4" t="n"/>
-      <c r="AC12" s="5" t="inlineStr"/>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" s="3" t="n"/>
       <c r="AD12" s="3" t="n"/>
       <c r="AE12" s="4" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="3" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="n"/>
@@ -2235,31 +2203,31 @@
       <c r="Q13" s="3" t="n"/>
       <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="n"/>
-      <c r="T13" s="4" t="n"/>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="5" t="inlineStr"/>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="4" t="n"/>
+      <c r="W13" s="5" t="inlineStr"/>
+      <c r="X13" s="3" t="n"/>
+      <c r="Y13" s="3" t="n"/>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="n"/>
-      <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="5" t="inlineStr"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="3" t="n"/>
       <c r="AD13" s="3" t="n"/>
       <c r="AE13" s="4" t="n"/>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="3" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="n"/>
@@ -2267,31 +2235,31 @@
       <c r="Q14" s="3" t="n"/>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
-      <c r="T14" s="4" t="n"/>
-      <c r="U14" s="5" t="inlineStr"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="5" t="inlineStr"/>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="4" t="n"/>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="3" t="n"/>
+      <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="4" t="n"/>
-      <c r="AC14" s="5" t="inlineStr"/>
+      <c r="AB14" s="3" t="n"/>
+      <c r="AC14" s="3" t="n"/>
       <c r="AD14" s="3" t="n"/>
       <c r="AE14" s="4" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="3" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="5" t="inlineStr"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="n"/>
@@ -2299,31 +2267,31 @@
       <c r="Q15" s="3" t="n"/>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3" t="n"/>
-      <c r="T15" s="4" t="n"/>
-      <c r="U15" s="5" t="inlineStr"/>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="5" t="inlineStr"/>
+      <c r="T15" s="3" t="n"/>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="4" t="n"/>
+      <c r="W15" s="5" t="inlineStr"/>
+      <c r="X15" s="3" t="n"/>
+      <c r="Y15" s="3" t="n"/>
       <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="5" t="inlineStr"/>
+      <c r="AB15" s="3" t="n"/>
+      <c r="AC15" s="3" t="n"/>
       <c r="AD15" s="3" t="n"/>
       <c r="AE15" s="4" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="3" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n"/>
@@ -2331,31 +2299,31 @@
       <c r="Q16" s="3" t="n"/>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
-      <c r="T16" s="4" t="n"/>
-      <c r="U16" s="5" t="inlineStr"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="5" t="inlineStr"/>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="4" t="n"/>
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="3" t="n"/>
+      <c r="Y16" s="3" t="n"/>
       <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="5" t="inlineStr"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="3" t="n"/>
       <c r="AD16" s="3" t="n"/>
       <c r="AE16" s="4" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="3" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="5" t="inlineStr"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n"/>
@@ -2363,31 +2331,31 @@
       <c r="Q17" s="3" t="n"/>
       <c r="R17" s="3" t="n"/>
       <c r="S17" s="3" t="n"/>
-      <c r="T17" s="4" t="n"/>
-      <c r="U17" s="5" t="inlineStr"/>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="4" t="n"/>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="3" t="n"/>
+      <c r="Y17" s="3" t="n"/>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="n"/>
-      <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="5" t="inlineStr"/>
+      <c r="AB17" s="3" t="n"/>
+      <c r="AC17" s="3" t="n"/>
       <c r="AD17" s="3" t="n"/>
       <c r="AE17" s="4" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="3" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="5" t="inlineStr"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="n"/>
@@ -2395,31 +2363,31 @@
       <c r="Q18" s="3" t="n"/>
       <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="n"/>
-      <c r="T18" s="4" t="n"/>
-      <c r="U18" s="5" t="inlineStr"/>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="T18" s="3" t="n"/>
+      <c r="U18" s="3" t="n"/>
+      <c r="V18" s="4" t="n"/>
+      <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="3" t="n"/>
+      <c r="Y18" s="3" t="n"/>
       <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="n"/>
-      <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="5" t="inlineStr"/>
+      <c r="AB18" s="3" t="n"/>
+      <c r="AC18" s="3" t="n"/>
       <c r="AD18" s="3" t="n"/>
       <c r="AE18" s="4" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="5" t="inlineStr"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
@@ -2427,119 +2395,234 @@
       <c r="Q19" s="3" t="n"/>
       <c r="R19" s="3" t="n"/>
       <c r="S19" s="3" t="n"/>
-      <c r="T19" s="4" t="n"/>
-      <c r="U19" s="5" t="inlineStr"/>
-      <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="4" t="n"/>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="3" t="n"/>
+      <c r="Y19" s="3" t="n"/>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="n"/>
-      <c r="AB19" s="4" t="n"/>
-      <c r="AC19" s="5" t="inlineStr"/>
+      <c r="AB19" s="3" t="n"/>
+      <c r="AC19" s="3" t="n"/>
       <c r="AD19" s="3" t="n"/>
       <c r="AE19" s="4" t="n"/>
     </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="3" t="n"/>
+      <c r="U20" s="3" t="n"/>
+      <c r="V20" s="4" t="n"/>
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="3" t="n"/>
+      <c r="Y20" s="3" t="n"/>
+      <c r="Z20" s="3" t="n"/>
+      <c r="AA20" s="3" t="n"/>
+      <c r="AB20" s="3" t="n"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n"/>
+      <c r="AE20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="4" t="n"/>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="3" t="n"/>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="3" t="n"/>
+      <c r="AD21" s="3" t="n"/>
+      <c r="AE21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n"/>
+      <c r="V22" s="4" t="n"/>
+      <c r="W22" s="5" t="inlineStr"/>
+      <c r="X22" s="3" t="n"/>
+      <c r="Y22" s="3" t="n"/>
+      <c r="Z22" s="3" t="n"/>
+      <c r="AA22" s="3" t="n"/>
+      <c r="AB22" s="3" t="n"/>
+      <c r="AC22" s="3" t="n"/>
+      <c r="AD22" s="3" t="n"/>
+      <c r="AE22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="4" t="n"/>
+      <c r="W23" s="5" t="inlineStr"/>
+      <c r="X23" s="3" t="n"/>
+      <c r="Y23" s="3" t="n"/>
+      <c r="Z23" s="3" t="n"/>
+      <c r="AA23" s="3" t="n"/>
+      <c r="AB23" s="3" t="n"/>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="3" t="n"/>
+      <c r="AE23" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="98">
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="AC14:AE14"/>
-    <mergeCell ref="Y12:AB12"/>
-    <mergeCell ref="L5:T5"/>
-    <mergeCell ref="L14:T14"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="L4:T4"/>
-    <mergeCell ref="Y4:AB4"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="AC16:AE16"/>
-    <mergeCell ref="L7:T7"/>
-    <mergeCell ref="Y10:AB10"/>
-    <mergeCell ref="L16:T16"/>
-    <mergeCell ref="Y19:AB19"/>
-    <mergeCell ref="AC18:AE18"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="Y18:AB18"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="U5:X5"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="U6:X6"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="L6:T6"/>
-    <mergeCell ref="AC12:AE12"/>
-    <mergeCell ref="AC7:AE7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="Y7:AB7"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="L18:T18"/>
-    <mergeCell ref="U8:X8"/>
-    <mergeCell ref="L8:T8"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="U10:X10"/>
-    <mergeCell ref="Y8:AB8"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="AC19:AE19"/>
-    <mergeCell ref="L10:T10"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="U9:X9"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="L9:T9"/>
-    <mergeCell ref="AC11:AE11"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="L11:T11"/>
-    <mergeCell ref="Y11:AB11"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="AC13:AE13"/>
-    <mergeCell ref="U7:X7"/>
-    <mergeCell ref="L13:T13"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="AC15:AE15"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="L15:T15"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="I18:K18"/>
+  <mergeCells count="85">
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="I6:V6"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="W3:AE3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="W14:AE14"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I8:V8"/>
+    <mergeCell ref="I17:V17"/>
+    <mergeCell ref="W6:AE6"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="I10:V10"/>
+    <mergeCell ref="I19:V19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="I9:V9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="I11:V11"/>
+    <mergeCell ref="W7:AE7"/>
+    <mergeCell ref="W16:AE16"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="W18:AE18"/>
+    <mergeCell ref="W8:AE8"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="W17:AE17"/>
+    <mergeCell ref="W11:AE11"/>
+    <mergeCell ref="I21:V21"/>
+    <mergeCell ref="W19:AE19"/>
+    <mergeCell ref="I23:V23"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="W5:AE5"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="W20:AE20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="W22:AE22"/>
+    <mergeCell ref="W12:AE12"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="W21:AE21"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="I22:V22"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="I3:V3"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="I12:V12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="I5:V5"/>
+    <mergeCell ref="I14:V14"/>
+    <mergeCell ref="W10:AE10"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="I4:V4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="I15:V15"/>
+    <mergeCell ref="D22:H22"/>
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="AC17:AE17"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="Y5:AB5"/>
-    <mergeCell ref="L17:T17"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="Y14:AB14"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="Y17:AB17"/>
-    <mergeCell ref="L19:T19"/>
-    <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="U12:X12"/>
-    <mergeCell ref="Y6:AB6"/>
-    <mergeCell ref="L12:T12"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I7:V7"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="I16:V16"/>
+    <mergeCell ref="W9:AE9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="I18:V18"/>
+    <mergeCell ref="W23:AE23"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="W13:AE13"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="W4:AE4"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="W15:AE15"/>
+    <mergeCell ref="I20:V20"/>
+    <mergeCell ref="I13:V13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2551,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AE24"/>
+  <dimension ref="B1:AE33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2590,844 +2673,1181 @@
     <row r="1" ht="36" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>詳細設計書 — インターフェース定義</t>
+          <t>詳細設計書 — 対象オブジェクト</t>
         </is>
       </c>
     </row>
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="26" customHeight="1">
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>■ インターフェース定義</t>
+          <t>オブジェクト名</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>コンポーネント</t>
+          <t>項目API名</t>
         </is>
       </c>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>項目ラベル</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="4" t="n"/>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>読み書き区分</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="4" t="n"/>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="n"/>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>メソッド/API名</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>入力パラメータ</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="6" t="inlineStr">
-        <is>
-          <t>返却値</t>
-        </is>
-      </c>
+      <c r="W4" s="4" t="n"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="n"/>
       <c r="AB4" s="3" t="n"/>
-      <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="6" t="inlineStr">
-        <is>
-          <t>例外</t>
-        </is>
-      </c>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="4" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="5" t="inlineStr"/>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
-      <c r="S5" s="4" t="n"/>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="3" t="n"/>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="3" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="W5" s="4" t="n"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="n"/>
       <c r="AB5" s="3" t="n"/>
-      <c r="AC5" s="4" t="n"/>
-      <c r="AD5" s="5" t="inlineStr"/>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="4" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="n"/>
       <c r="R6" s="3" t="n"/>
-      <c r="S6" s="4" t="n"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="5" t="inlineStr"/>
       <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" s="3" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="W6" s="4" t="n"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
       <c r="AA6" s="3" t="n"/>
       <c r="AB6" s="3" t="n"/>
-      <c r="AC6" s="4" t="n"/>
-      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
       <c r="AE6" s="4" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="5" t="inlineStr"/>
       <c r="P7" s="3" t="n"/>
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
-      <c r="S7" s="4" t="n"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="4" t="n"/>
+      <c r="U7" s="5" t="inlineStr"/>
       <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="3" t="n"/>
+      <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="n"/>
       <c r="AB7" s="3" t="n"/>
-      <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="5" t="inlineStr"/>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="3" t="n"/>
       <c r="AE7" s="4" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="5" t="inlineStr"/>
       <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="W8" s="4" t="n"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="3" t="n"/>
+      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="n"/>
       <c r="AB8" s="3" t="n"/>
-      <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="5" t="inlineStr"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
       <c r="AE8" s="4" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n"/>
       <c r="R9" s="3" t="n"/>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="4" t="n"/>
+      <c r="U9" s="5" t="inlineStr"/>
       <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="3" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="W9" s="4" t="n"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="3" t="n"/>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="n"/>
       <c r="AB9" s="3" t="n"/>
-      <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="5" t="inlineStr"/>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="3" t="n"/>
       <c r="AE9" s="4" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="5" t="inlineStr"/>
       <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="5" t="inlineStr"/>
       <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="W10" s="4" t="n"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="n"/>
       <c r="AB10" s="3" t="n"/>
-      <c r="AC10" s="4" t="n"/>
-      <c r="AD10" s="5" t="inlineStr"/>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="3" t="n"/>
       <c r="AE10" s="4" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="5" t="inlineStr"/>
       <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="W11" s="4" t="n"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="n"/>
       <c r="AB11" s="3" t="n"/>
-      <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="5" t="inlineStr"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
       <c r="AE11" s="4" t="n"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="3" t="n"/>
       <c r="Q12" s="3" t="n"/>
       <c r="R12" s="3" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="5" t="inlineStr"/>
       <c r="V12" s="3" t="n"/>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="3" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="5" t="inlineStr"/>
+      <c r="W12" s="4" t="n"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="n"/>
       <c r="AB12" s="3" t="n"/>
-      <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="5" t="inlineStr"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
       <c r="AE12" s="4" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="n"/>
       <c r="R13" s="3" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="4" t="n"/>
+      <c r="U13" s="5" t="inlineStr"/>
       <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="5" t="inlineStr"/>
+      <c r="W13" s="4" t="n"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="n"/>
       <c r="AB13" s="3" t="n"/>
-      <c r="AC13" s="4" t="n"/>
-      <c r="AD13" s="5" t="inlineStr"/>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="3" t="n"/>
       <c r="AE13" s="4" t="n"/>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n"/>
       <c r="R14" s="3" t="n"/>
-      <c r="S14" s="4" t="n"/>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="5" t="inlineStr"/>
       <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="W14" s="4" t="n"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="3" t="n"/>
+      <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="n"/>
       <c r="AB14" s="3" t="n"/>
-      <c r="AC14" s="4" t="n"/>
-      <c r="AD14" s="5" t="inlineStr"/>
+      <c r="AC14" s="3" t="n"/>
+      <c r="AD14" s="3" t="n"/>
       <c r="AE14" s="4" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="5" t="inlineStr"/>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n"/>
       <c r="R15" s="3" t="n"/>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="5" t="inlineStr"/>
-      <c r="U15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="5" t="inlineStr"/>
       <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="5" t="inlineStr"/>
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="5" t="inlineStr"/>
+      <c r="Y15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="n"/>
       <c r="AB15" s="3" t="n"/>
-      <c r="AC15" s="4" t="n"/>
-      <c r="AD15" s="5" t="inlineStr"/>
+      <c r="AC15" s="3" t="n"/>
+      <c r="AD15" s="3" t="n"/>
       <c r="AE15" s="4" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n"/>
       <c r="R16" s="3" t="n"/>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="5" t="inlineStr"/>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="n"/>
       <c r="AB16" s="3" t="n"/>
-      <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="5" t="inlineStr"/>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="3" t="n"/>
       <c r="AE16" s="4" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="5" t="inlineStr"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="5" t="inlineStr"/>
       <c r="P17" s="3" t="n"/>
       <c r="Q17" s="3" t="n"/>
       <c r="R17" s="3" t="n"/>
-      <c r="S17" s="4" t="n"/>
-      <c r="T17" s="5" t="inlineStr"/>
-      <c r="U17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="5" t="inlineStr"/>
       <c r="V17" s="3" t="n"/>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" s="3" t="n"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="5" t="inlineStr"/>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="3" t="n"/>
+      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="n"/>
       <c r="AB17" s="3" t="n"/>
-      <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="5" t="inlineStr"/>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="3" t="n"/>
       <c r="AE17" s="4" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="n"/>
       <c r="R18" s="3" t="n"/>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="5" t="inlineStr"/>
+      <c r="W18" s="4" t="n"/>
+      <c r="X18" s="5" t="inlineStr"/>
+      <c r="Y18" s="3" t="n"/>
+      <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="n"/>
       <c r="AB18" s="3" t="n"/>
-      <c r="AC18" s="4" t="n"/>
-      <c r="AD18" s="5" t="inlineStr"/>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="3" t="n"/>
       <c r="AE18" s="4" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n"/>
       <c r="R19" s="3" t="n"/>
-      <c r="S19" s="4" t="n"/>
-      <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="3" t="n"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="5" t="inlineStr"/>
+      <c r="W19" s="4" t="n"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="3" t="n"/>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="n"/>
       <c r="AB19" s="3" t="n"/>
-      <c r="AC19" s="4" t="n"/>
-      <c r="AD19" s="5" t="inlineStr"/>
+      <c r="AC19" s="3" t="n"/>
+      <c r="AD19" s="3" t="n"/>
       <c r="AE19" s="4" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="22" customHeight="1">
       <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="5" t="inlineStr"/>
       <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="n"/>
       <c r="R20" s="3" t="n"/>
-      <c r="S20" s="4" t="n"/>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="3" t="n"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="5" t="inlineStr"/>
       <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
-      <c r="X20" s="3" t="n"/>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="W20" s="4" t="n"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="3" t="n"/>
+      <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="n"/>
       <c r="AB20" s="3" t="n"/>
-      <c r="AC20" s="4" t="n"/>
-      <c r="AD20" s="5" t="inlineStr"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n"/>
       <c r="AE20" s="4" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="22" customHeight="1">
       <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="3" t="n"/>
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="n"/>
-      <c r="S21" s="4" t="n"/>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="3" t="n"/>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="3" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="W21" s="4" t="n"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="n"/>
       <c r="AB21" s="3" t="n"/>
-      <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="5" t="inlineStr"/>
+      <c r="AC21" s="3" t="n"/>
+      <c r="AD21" s="3" t="n"/>
       <c r="AE21" s="4" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="22" customHeight="1">
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="n"/>
       <c r="R22" s="3" t="n"/>
-      <c r="S22" s="4" t="n"/>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="3" t="n"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="3" t="n"/>
-      <c r="W22" s="3" t="n"/>
-      <c r="X22" s="3" t="n"/>
-      <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="5" t="inlineStr"/>
+      <c r="W22" s="4" t="n"/>
+      <c r="X22" s="5" t="inlineStr"/>
+      <c r="Y22" s="3" t="n"/>
+      <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="n"/>
       <c r="AB22" s="3" t="n"/>
-      <c r="AC22" s="4" t="n"/>
-      <c r="AD22" s="5" t="inlineStr"/>
+      <c r="AC22" s="3" t="n"/>
+      <c r="AD22" s="3" t="n"/>
       <c r="AE22" s="4" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="22" customHeight="1">
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="n"/>
       <c r="R23" s="3" t="n"/>
-      <c r="S23" s="4" t="n"/>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="5" t="inlineStr"/>
       <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
-      <c r="Y23" s="4" t="n"/>
-      <c r="Z23" s="5" t="inlineStr"/>
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="5" t="inlineStr"/>
+      <c r="Y23" s="3" t="n"/>
+      <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="n"/>
       <c r="AB23" s="3" t="n"/>
-      <c r="AC23" s="4" t="n"/>
-      <c r="AD23" s="5" t="inlineStr"/>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="3" t="n"/>
       <c r="AE23" s="4" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="22" customHeight="1">
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n"/>
-      <c r="S24" s="4" t="n"/>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="3" t="n"/>
+      <c r="S24" s="3" t="n"/>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="5" t="inlineStr"/>
       <c r="V24" s="3" t="n"/>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="3" t="n"/>
-      <c r="Y24" s="4" t="n"/>
-      <c r="Z24" s="5" t="inlineStr"/>
+      <c r="W24" s="4" t="n"/>
+      <c r="X24" s="5" t="inlineStr"/>
+      <c r="Y24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="n"/>
       <c r="AB24" s="3" t="n"/>
-      <c r="AC24" s="4" t="n"/>
-      <c r="AD24" s="5" t="inlineStr"/>
+      <c r="AC24" s="3" t="n"/>
+      <c r="AD24" s="3" t="n"/>
       <c r="AE24" s="4" t="n"/>
     </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="3" t="n"/>
+      <c r="W25" s="4" t="n"/>
+      <c r="X25" s="5" t="inlineStr"/>
+      <c r="Y25" s="3" t="n"/>
+      <c r="Z25" s="3" t="n"/>
+      <c r="AA25" s="3" t="n"/>
+      <c r="AB25" s="3" t="n"/>
+      <c r="AC25" s="3" t="n"/>
+      <c r="AD25" s="3" t="n"/>
+      <c r="AE25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="3" t="n"/>
+      <c r="W26" s="4" t="n"/>
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="3" t="n"/>
+      <c r="Z26" s="3" t="n"/>
+      <c r="AA26" s="3" t="n"/>
+      <c r="AB26" s="3" t="n"/>
+      <c r="AC26" s="3" t="n"/>
+      <c r="AD26" s="3" t="n"/>
+      <c r="AE26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="4" t="n"/>
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="3" t="n"/>
+      <c r="W27" s="4" t="n"/>
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="3" t="n"/>
+      <c r="Z27" s="3" t="n"/>
+      <c r="AA27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" s="3" t="n"/>
+      <c r="AD27" s="3" t="n"/>
+      <c r="AE27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="3" t="n"/>
+      <c r="W28" s="4" t="n"/>
+      <c r="X28" s="5" t="inlineStr"/>
+      <c r="Y28" s="3" t="n"/>
+      <c r="Z28" s="3" t="n"/>
+      <c r="AA28" s="3" t="n"/>
+      <c r="AB28" s="3" t="n"/>
+      <c r="AC28" s="3" t="n"/>
+      <c r="AD28" s="3" t="n"/>
+      <c r="AE28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="3" t="n"/>
+      <c r="T29" s="4" t="n"/>
+      <c r="U29" s="5" t="inlineStr"/>
+      <c r="V29" s="3" t="n"/>
+      <c r="W29" s="4" t="n"/>
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n"/>
+      <c r="AA29" s="3" t="n"/>
+      <c r="AB29" s="3" t="n"/>
+      <c r="AC29" s="3" t="n"/>
+      <c r="AD29" s="3" t="n"/>
+      <c r="AE29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="5" t="inlineStr"/>
+      <c r="V30" s="3" t="n"/>
+      <c r="W30" s="4" t="n"/>
+      <c r="X30" s="5" t="inlineStr"/>
+      <c r="Y30" s="3" t="n"/>
+      <c r="Z30" s="3" t="n"/>
+      <c r="AA30" s="3" t="n"/>
+      <c r="AB30" s="3" t="n"/>
+      <c r="AC30" s="3" t="n"/>
+      <c r="AD30" s="3" t="n"/>
+      <c r="AE30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
+      <c r="R31" s="3" t="n"/>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="4" t="n"/>
+      <c r="U31" s="5" t="inlineStr"/>
+      <c r="V31" s="3" t="n"/>
+      <c r="W31" s="4" t="n"/>
+      <c r="X31" s="5" t="inlineStr"/>
+      <c r="Y31" s="3" t="n"/>
+      <c r="Z31" s="3" t="n"/>
+      <c r="AA31" s="3" t="n"/>
+      <c r="AB31" s="3" t="n"/>
+      <c r="AC31" s="3" t="n"/>
+      <c r="AD31" s="3" t="n"/>
+      <c r="AE31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="3" t="n"/>
+      <c r="Q32" s="3" t="n"/>
+      <c r="R32" s="3" t="n"/>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="3" t="n"/>
+      <c r="W32" s="4" t="n"/>
+      <c r="X32" s="5" t="inlineStr"/>
+      <c r="Y32" s="3" t="n"/>
+      <c r="Z32" s="3" t="n"/>
+      <c r="AA32" s="3" t="n"/>
+      <c r="AB32" s="3" t="n"/>
+      <c r="AC32" s="3" t="n"/>
+      <c r="AD32" s="3" t="n"/>
+      <c r="AE32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="3" t="n"/>
+      <c r="W33" s="4" t="n"/>
+      <c r="X33" s="5" t="inlineStr"/>
+      <c r="Y33" s="3" t="n"/>
+      <c r="Z33" s="3" t="n"/>
+      <c r="AA33" s="3" t="n"/>
+      <c r="AB33" s="3" t="n"/>
+      <c r="AC33" s="3" t="n"/>
+      <c r="AD33" s="3" t="n"/>
+      <c r="AE33" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="128">
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="Z10:AC10"/>
-    <mergeCell ref="Z19:AC19"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="M19:S19"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="T8:Y8"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="T16:Y16"/>
-    <mergeCell ref="Z11:AC11"/>
-    <mergeCell ref="T18:Y18"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="AD16:AE16"/>
-    <mergeCell ref="Z21:AC21"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="M7:S7"/>
-    <mergeCell ref="M21:S21"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="Z23:AC23"/>
-    <mergeCell ref="AD8:AE8"/>
-    <mergeCell ref="Z13:AC13"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="M24:S24"/>
-    <mergeCell ref="T12:Y12"/>
-    <mergeCell ref="Z15:AC15"/>
-    <mergeCell ref="T21:Y21"/>
-    <mergeCell ref="Z24:AC24"/>
-    <mergeCell ref="T23:Y23"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="T13:Y13"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="T7:Y7"/>
-    <mergeCell ref="M9:S9"/>
-    <mergeCell ref="M5:S5"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="M11:S11"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="Z22:AC22"/>
-    <mergeCell ref="Z12:AC12"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="M15:S15"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="Z5:AC5"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="Z14:AC14"/>
-    <mergeCell ref="T9:Y9"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="M23:S23"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="T11:Y11"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="AD11:AE11"/>
-    <mergeCell ref="Z16:AC16"/>
-    <mergeCell ref="M20:S20"/>
-    <mergeCell ref="T15:Y15"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="T24:Y24"/>
-    <mergeCell ref="Z18:AC18"/>
-    <mergeCell ref="M22:S22"/>
-    <mergeCell ref="Z8:AC8"/>
-    <mergeCell ref="Z17:AC17"/>
-    <mergeCell ref="M6:S6"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AD9:AE9"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="T10:Y10"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="Z20:AC20"/>
-    <mergeCell ref="AD14:AE14"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="M14:S14"/>
-    <mergeCell ref="AD13:AE13"/>
+  <mergeCells count="156">
+    <mergeCell ref="X12:AE12"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="X21:AE21"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="X23:AE23"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="X13:AE13"/>
+    <mergeCell ref="X7:AE7"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="O12:T12"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="O14:T14"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="O23:T23"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="X33:AE33"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O13:T13"/>
+    <mergeCell ref="O7:T7"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="O15:T15"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="X25:AE25"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="X9:AE9"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="X27:AE27"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="X11:AE11"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="O25:T25"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O27:T27"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="O11:T11"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="X6:AE6"/>
+    <mergeCell ref="X15:AE15"/>
+    <mergeCell ref="X24:AE24"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="U26:W26"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="X26:AE26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="X10:AE10"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="O32:T32"/>
+    <mergeCell ref="O26:T26"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="X17:AE17"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U28:W28"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="X19:AE19"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="X28:AE28"/>
+    <mergeCell ref="O8:T8"/>
+    <mergeCell ref="X3:AE3"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="U23:W23"/>
+    <mergeCell ref="X30:AE30"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="X20:AE20"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="X14:AE14"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="X29:AE29"/>
+    <mergeCell ref="U31:W31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="X4:AE4"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="O28:T28"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="O9:T9"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="O30:T30"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="O29:T29"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="X32:AE32"/>
+    <mergeCell ref="O31:T31"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="X8:AE8"/>
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="T17:Y17"/>
-    <mergeCell ref="Z6:AC6"/>
-    <mergeCell ref="AD15:AE15"/>
-    <mergeCell ref="T22:Y22"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="T6:Y6"/>
-    <mergeCell ref="T19:Y19"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="M10:S10"/>
-    <mergeCell ref="T5:Y5"/>
-    <mergeCell ref="T20:Y20"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="T14:Y14"/>
-    <mergeCell ref="M16:S16"/>
-    <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="T4:Y4"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="O21:T21"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="X16:AE16"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="X18:AE18"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="U5:W5"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="O10:T10"/>
+    <mergeCell ref="O24:T24"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="O33:T33"/>
+    <mergeCell ref="X22:AE22"/>
+    <mergeCell ref="X31:AE31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3439,7 +3859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AE19"/>
+  <dimension ref="B1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3478,76 +3898,89 @@
     <row r="1" ht="36" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>詳細設計書 — 画面仕様</t>
+          <t>詳細設計書 — 処理概要</t>
         </is>
       </c>
     </row>
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="26" customHeight="1">
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>■ {画面名}</t>
+          <t>ステップNo</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>処理内容</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>項目名</t>
+          <t>条件分岐</t>
         </is>
       </c>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>SOQL概要</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="3" t="n"/>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="4" t="n"/>
+      <c r="Z3" s="6" t="inlineStr">
+        <is>
+          <t>DML操作</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>API名/プロパティ</t>
-        </is>
-      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>UI種別</t>
-        </is>
-      </c>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
       <c r="S4" s="4" t="n"/>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n"/>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>初期値</t>
-        </is>
-      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="6" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="4" t="n"/>
+      <c r="Z4" s="5" t="inlineStr"/>
       <c r="AA4" s="3" t="n"/>
       <c r="AB4" s="3" t="n"/>
       <c r="AC4" s="3" t="n"/>
@@ -3561,21 +3994,872 @@
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="5" t="inlineStr"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="5" t="inlineStr"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="5" t="inlineStr"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AE6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="4" t="n"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" s="3" t="n"/>
+      <c r="X7" s="3" t="n"/>
+      <c r="Y7" s="4" t="n"/>
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="3" t="n"/>
+      <c r="AE7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" s="3" t="n"/>
+      <c r="X8" s="3" t="n"/>
+      <c r="Y8" s="4" t="n"/>
+      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="AA8" s="3" t="n"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AE8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="4" t="n"/>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="n"/>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" s="4" t="n"/>
+      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="AA9" s="3" t="n"/>
+      <c r="AB9" s="3" t="n"/>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="3" t="n"/>
+      <c r="AE9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="4" t="n"/>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="3" t="n"/>
+      <c r="X10" s="3" t="n"/>
+      <c r="Y10" s="4" t="n"/>
+      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="AA10" s="3" t="n"/>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="3" t="n"/>
+      <c r="AE10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="4" t="n"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="4" t="n"/>
+      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="AA11" s="3" t="n"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="4" t="n"/>
+      <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
+      <c r="W12" s="3" t="n"/>
+      <c r="X12" s="3" t="n"/>
+      <c r="Y12" s="4" t="n"/>
+      <c r="Z12" s="5" t="inlineStr"/>
+      <c r="AA12" s="3" t="n"/>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AE12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n"/>
+      <c r="X13" s="3" t="n"/>
+      <c r="Y13" s="4" t="n"/>
+      <c r="Z13" s="5" t="inlineStr"/>
+      <c r="AA13" s="3" t="n"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="3" t="n"/>
+      <c r="AE13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
+      <c r="W14" s="3" t="n"/>
+      <c r="X14" s="3" t="n"/>
+      <c r="Y14" s="4" t="n"/>
+      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="AA14" s="3" t="n"/>
+      <c r="AB14" s="3" t="n"/>
+      <c r="AC14" s="3" t="n"/>
+      <c r="AD14" s="3" t="n"/>
+      <c r="AE14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="4" t="n"/>
+      <c r="T15" s="5" t="inlineStr"/>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n"/>
+      <c r="W15" s="3" t="n"/>
+      <c r="X15" s="3" t="n"/>
+      <c r="Y15" s="4" t="n"/>
+      <c r="Z15" s="5" t="inlineStr"/>
+      <c r="AA15" s="3" t="n"/>
+      <c r="AB15" s="3" t="n"/>
+      <c r="AC15" s="3" t="n"/>
+      <c r="AD15" s="3" t="n"/>
+      <c r="AE15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="4" t="n"/>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
+      <c r="Y16" s="4" t="n"/>
+      <c r="Z16" s="5" t="inlineStr"/>
+      <c r="AA16" s="3" t="n"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="3" t="n"/>
+      <c r="AE16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="5" t="inlineStr"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="3" t="n"/>
+      <c r="W17" s="3" t="n"/>
+      <c r="X17" s="3" t="n"/>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="5" t="inlineStr"/>
+      <c r="AA17" s="3" t="n"/>
+      <c r="AB17" s="3" t="n"/>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="3" t="n"/>
+      <c r="AE17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="3" t="n"/>
+      <c r="V18" s="3" t="n"/>
+      <c r="W18" s="3" t="n"/>
+      <c r="X18" s="3" t="n"/>
+      <c r="Y18" s="4" t="n"/>
+      <c r="Z18" s="5" t="inlineStr"/>
+      <c r="AA18" s="3" t="n"/>
+      <c r="AB18" s="3" t="n"/>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="3" t="n"/>
+      <c r="AE18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="4" t="n"/>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="3" t="n"/>
+      <c r="W19" s="3" t="n"/>
+      <c r="X19" s="3" t="n"/>
+      <c r="Y19" s="4" t="n"/>
+      <c r="Z19" s="5" t="inlineStr"/>
+      <c r="AA19" s="3" t="n"/>
+      <c r="AB19" s="3" t="n"/>
+      <c r="AC19" s="3" t="n"/>
+      <c r="AD19" s="3" t="n"/>
+      <c r="AE19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="4" t="n"/>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="3" t="n"/>
+      <c r="V20" s="3" t="n"/>
+      <c r="W20" s="3" t="n"/>
+      <c r="X20" s="3" t="n"/>
+      <c r="Y20" s="4" t="n"/>
+      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="AA20" s="3" t="n"/>
+      <c r="AB20" s="3" t="n"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n"/>
+      <c r="AE20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="3" t="n"/>
+      <c r="W21" s="3" t="n"/>
+      <c r="X21" s="3" t="n"/>
+      <c r="Y21" s="4" t="n"/>
+      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="3" t="n"/>
+      <c r="AD21" s="3" t="n"/>
+      <c r="AE21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="4" t="n"/>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="3" t="n"/>
+      <c r="V22" s="3" t="n"/>
+      <c r="W22" s="3" t="n"/>
+      <c r="X22" s="3" t="n"/>
+      <c r="Y22" s="4" t="n"/>
+      <c r="Z22" s="5" t="inlineStr"/>
+      <c r="AA22" s="3" t="n"/>
+      <c r="AB22" s="3" t="n"/>
+      <c r="AC22" s="3" t="n"/>
+      <c r="AD22" s="3" t="n"/>
+      <c r="AE22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="4" t="n"/>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n"/>
+      <c r="X23" s="3" t="n"/>
+      <c r="Y23" s="4" t="n"/>
+      <c r="Z23" s="5" t="inlineStr"/>
+      <c r="AA23" s="3" t="n"/>
+      <c r="AB23" s="3" t="n"/>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="3" t="n"/>
+      <c r="AE23" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="106">
+    <mergeCell ref="Z7:AE7"/>
+    <mergeCell ref="D12:M12"/>
+    <mergeCell ref="D9:M9"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N18:S18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="D14:M14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D23:M23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="T8:Y8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="T16:Y16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="Z19:AE19"/>
+    <mergeCell ref="T18:Y18"/>
+    <mergeCell ref="Z9:AE9"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="Z11:AE11"/>
+    <mergeCell ref="D17:M17"/>
+    <mergeCell ref="N22:S22"/>
+    <mergeCell ref="N3:S3"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:M3"/>
+    <mergeCell ref="N5:S5"/>
+    <mergeCell ref="N14:S14"/>
+    <mergeCell ref="Z21:AE21"/>
+    <mergeCell ref="T12:Y12"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="T21:Y21"/>
+    <mergeCell ref="D5:M5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="Z23:AE23"/>
+    <mergeCell ref="T23:Y23"/>
+    <mergeCell ref="Z13:AE13"/>
+    <mergeCell ref="T13:Y13"/>
+    <mergeCell ref="T7:Y7"/>
+    <mergeCell ref="Z15:AE15"/>
+    <mergeCell ref="D21:M21"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="N16:S16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="D16:M16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D18:M18"/>
+    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="T9:Y9"/>
+    <mergeCell ref="D8:M8"/>
+    <mergeCell ref="Z3:AE3"/>
+    <mergeCell ref="Z12:AE12"/>
+    <mergeCell ref="T11:Y11"/>
+    <mergeCell ref="Z5:AE5"/>
+    <mergeCell ref="Z14:AE14"/>
+    <mergeCell ref="N13:S13"/>
+    <mergeCell ref="D20:M20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="Z4:AE4"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="D22:M22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D13:M13"/>
+    <mergeCell ref="T15:Y15"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="Z16:AE16"/>
+    <mergeCell ref="T10:Y10"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="Z18:AE18"/>
+    <mergeCell ref="D15:M15"/>
+    <mergeCell ref="N17:S17"/>
+    <mergeCell ref="Z8:AE8"/>
+    <mergeCell ref="Z17:AE17"/>
+    <mergeCell ref="B1:AE1"/>
+    <mergeCell ref="N19:S19"/>
+    <mergeCell ref="T17:Y17"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="T22:Y22"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="D10:M10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="Z20:AE20"/>
+    <mergeCell ref="D19:M19"/>
+    <mergeCell ref="T6:Y6"/>
+    <mergeCell ref="T19:Y19"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="T3:Y3"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="Z6:AE6"/>
+    <mergeCell ref="D11:M11"/>
+    <mergeCell ref="T5:Y5"/>
+    <mergeCell ref="T20:Y20"/>
+    <mergeCell ref="T14:Y14"/>
+    <mergeCell ref="T4:Y4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:AE18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="4.2" customWidth="1" min="2" max="2"/>
+    <col width="4.2" customWidth="1" min="3" max="3"/>
+    <col width="4.2" customWidth="1" min="4" max="4"/>
+    <col width="4.2" customWidth="1" min="5" max="5"/>
+    <col width="4.2" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>詳細設計書 — 関連コンポーネント</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>コンポーネント名</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="3" t="n"/>
+      <c r="X3" s="4" t="n"/>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>依存方向</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" s="3" t="n"/>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="4" t="n"/>
+      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="n"/>
       <c r="X5" s="4" t="n"/>
       <c r="Y5" s="5" t="inlineStr"/>
@@ -3588,26 +4872,26 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="5" t="inlineStr"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="4" t="n"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="4" t="n"/>
-      <c r="V6" s="5" t="inlineStr"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
       <c r="W6" s="3" t="n"/>
       <c r="X6" s="4" t="n"/>
       <c r="Y6" s="5" t="inlineStr"/>
@@ -3620,26 +4904,26 @@
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="5" t="inlineStr"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="4" t="n"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="4" t="n"/>
-      <c r="V7" s="5" t="inlineStr"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="n"/>
       <c r="X7" s="4" t="n"/>
       <c r="Y7" s="5" t="inlineStr"/>
@@ -3652,26 +4936,26 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="5" t="inlineStr"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="4" t="n"/>
-      <c r="V8" s="5" t="inlineStr"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
       <c r="W8" s="3" t="n"/>
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="5" t="inlineStr"/>
@@ -3684,26 +4968,26 @@
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="5" t="inlineStr"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="4" t="n"/>
-      <c r="V9" s="5" t="inlineStr"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="4" t="n"/>
       <c r="Y9" s="5" t="inlineStr"/>
@@ -3716,26 +5000,26 @@
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="5" t="inlineStr"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="4" t="n"/>
-      <c r="V10" s="5" t="inlineStr"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n"/>
       <c r="X10" s="4" t="n"/>
       <c r="Y10" s="5" t="inlineStr"/>
@@ -3748,26 +5032,26 @@
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="5" t="inlineStr"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="5" t="inlineStr"/>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="4" t="n"/>
-      <c r="V11" s="5" t="inlineStr"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="4" t="n"/>
       <c r="Y11" s="5" t="inlineStr"/>
@@ -3780,26 +5064,26 @@
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="5" t="inlineStr"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="3" t="n"/>
       <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="5" t="inlineStr"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="4" t="n"/>
-      <c r="V12" s="5" t="inlineStr"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="4" t="n"/>
       <c r="Y12" s="5" t="inlineStr"/>
@@ -3812,26 +5096,26 @@
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="5" t="inlineStr"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="4" t="n"/>
-      <c r="V13" s="5" t="inlineStr"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
       <c r="W13" s="3" t="n"/>
       <c r="X13" s="4" t="n"/>
       <c r="Y13" s="5" t="inlineStr"/>
@@ -3844,26 +5128,26 @@
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="5" t="inlineStr"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="5" t="inlineStr"/>
-      <c r="S14" s="4" t="n"/>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="4" t="n"/>
-      <c r="V14" s="5" t="inlineStr"/>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
       <c r="W14" s="3" t="n"/>
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="5" t="inlineStr"/>
@@ -3876,26 +5160,26 @@
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="5" t="inlineStr"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="5" t="inlineStr"/>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="5" t="inlineStr"/>
-      <c r="U15" s="4" t="n"/>
-      <c r="V15" s="5" t="inlineStr"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n"/>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n"/>
       <c r="W15" s="3" t="n"/>
       <c r="X15" s="4" t="n"/>
       <c r="Y15" s="5" t="inlineStr"/>
@@ -3908,26 +5192,26 @@
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="5" t="inlineStr"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="3" t="n"/>
       <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="4" t="n"/>
-      <c r="V16" s="5" t="inlineStr"/>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
       <c r="W16" s="3" t="n"/>
       <c r="X16" s="4" t="n"/>
       <c r="Y16" s="5" t="inlineStr"/>
@@ -3940,26 +5224,26 @@
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="5" t="inlineStr"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="5" t="inlineStr"/>
-      <c r="S17" s="4" t="n"/>
-      <c r="T17" s="5" t="inlineStr"/>
-      <c r="U17" s="4" t="n"/>
-      <c r="V17" s="5" t="inlineStr"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="3" t="n"/>
       <c r="W17" s="3" t="n"/>
       <c r="X17" s="4" t="n"/>
       <c r="Y17" s="5" t="inlineStr"/>
@@ -3972,26 +5256,26 @@
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="5" t="inlineStr"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="3" t="n"/>
       <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="5" t="inlineStr"/>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="4" t="n"/>
-      <c r="V18" s="5" t="inlineStr"/>
+      <c r="Q18" s="3" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="3" t="n"/>
+      <c r="U18" s="3" t="n"/>
+      <c r="V18" s="3" t="n"/>
       <c r="W18" s="3" t="n"/>
       <c r="X18" s="4" t="n"/>
       <c r="Y18" s="5" t="inlineStr"/>
@@ -4002,31 +5286,608 @@
       <c r="AD18" s="3" t="n"/>
       <c r="AE18" s="4" t="n"/>
     </row>
+  </sheetData>
+  <mergeCells count="65">
+    <mergeCell ref="Y13:AE13"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="N4:X4"/>
+    <mergeCell ref="Y18:AE18"/>
+    <mergeCell ref="N11:X11"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="Y12:AE12"/>
+    <mergeCell ref="N16:X16"/>
+    <mergeCell ref="Y6:AE6"/>
+    <mergeCell ref="N7:X7"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B1:AE1"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="Y8:AE8"/>
+    <mergeCell ref="N3:X3"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="N12:X12"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="N18:X18"/>
+    <mergeCell ref="Y3:AE3"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="N5:X5"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="N8:X8"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="N14:X14"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="Y15:AE15"/>
+    <mergeCell ref="N17:X17"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="Y9:AE9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="N10:X10"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Y14:AE14"/>
+    <mergeCell ref="Y5:AE5"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="Y11:AE11"/>
+    <mergeCell ref="N13:X13"/>
+    <mergeCell ref="Y10:AE10"/>
+    <mergeCell ref="N9:X9"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="Y17:AE17"/>
+    <mergeCell ref="N6:X6"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="Y7:AE7"/>
+    <mergeCell ref="N15:X15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="Y16:AE16"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="B4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:AE50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="4.2" customWidth="1" min="2" max="2"/>
+    <col width="4.2" customWidth="1" min="3" max="3"/>
+    <col width="4.2" customWidth="1" min="4" max="4"/>
+    <col width="4.2" customWidth="1" min="5" max="5"/>
+    <col width="4.2" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>詳細設計書 — 影響範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>■ 更新オブジェクト</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>オブジェクト名</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>更新項目</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>更新条件</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="3" t="n"/>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AE6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="4" t="n"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" s="3" t="n"/>
+      <c r="X7" s="3" t="n"/>
+      <c r="Y7" s="3" t="n"/>
+      <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="3" t="n"/>
+      <c r="AE7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" s="3" t="n"/>
+      <c r="X8" s="3" t="n"/>
+      <c r="Y8" s="3" t="n"/>
+      <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AE8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="4" t="n"/>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="n"/>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" s="3" t="n"/>
+      <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
+      <c r="AB9" s="3" t="n"/>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="3" t="n"/>
+      <c r="AE9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="3" t="n"/>
+      <c r="X10" s="3" t="n"/>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="3" t="n"/>
+      <c r="AE10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="3" t="n"/>
+      <c r="W12" s="3" t="n"/>
+      <c r="X12" s="3" t="n"/>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AE12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1"/>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>■ 参照オブジェクト</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>オブジェクト名</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>参照項目</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>参照目的</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="n"/>
+      <c r="W15" s="3" t="n"/>
+      <c r="X15" s="3" t="n"/>
+      <c r="Y15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
+      <c r="AA15" s="3" t="n"/>
+      <c r="AB15" s="3" t="n"/>
+      <c r="AC15" s="3" t="n"/>
+      <c r="AD15" s="3" t="n"/>
+      <c r="AE15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
+      <c r="Y16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n"/>
+      <c r="AA16" s="3" t="n"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="3" t="n"/>
+      <c r="AE16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="3" t="n"/>
+      <c r="W17" s="3" t="n"/>
+      <c r="X17" s="3" t="n"/>
+      <c r="Y17" s="3" t="n"/>
+      <c r="Z17" s="3" t="n"/>
+      <c r="AA17" s="3" t="n"/>
+      <c r="AB17" s="3" t="n"/>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="3" t="n"/>
+      <c r="AE17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="3" t="n"/>
+      <c r="W18" s="3" t="n"/>
+      <c r="X18" s="3" t="n"/>
+      <c r="Y18" s="3" t="n"/>
+      <c r="Z18" s="3" t="n"/>
+      <c r="AA18" s="3" t="n"/>
+      <c r="AB18" s="3" t="n"/>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="3" t="n"/>
+      <c r="AE18" s="4" t="n"/>
+    </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="5" t="inlineStr"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="5" t="inlineStr"/>
-      <c r="S19" s="4" t="n"/>
-      <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="4" t="n"/>
-      <c r="V19" s="5" t="inlineStr"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="3" t="n"/>
       <c r="W19" s="3" t="n"/>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="X19" s="3" t="n"/>
+      <c r="Y19" s="3" t="n"/>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="n"/>
       <c r="AB19" s="3" t="n"/>
@@ -4034,138 +5895,972 @@
       <c r="AD19" s="3" t="n"/>
       <c r="AE19" s="4" t="n"/>
     </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="5" t="inlineStr"/>
+      <c r="V20" s="3" t="n"/>
+      <c r="W20" s="3" t="n"/>
+      <c r="X20" s="3" t="n"/>
+      <c r="Y20" s="3" t="n"/>
+      <c r="Z20" s="3" t="n"/>
+      <c r="AA20" s="3" t="n"/>
+      <c r="AB20" s="3" t="n"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n"/>
+      <c r="AE20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="3" t="n"/>
+      <c r="W21" s="3" t="n"/>
+      <c r="X21" s="3" t="n"/>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="3" t="n"/>
+      <c r="AD21" s="3" t="n"/>
+      <c r="AE21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="5" t="inlineStr"/>
+      <c r="V22" s="3" t="n"/>
+      <c r="W22" s="3" t="n"/>
+      <c r="X22" s="3" t="n"/>
+      <c r="Y22" s="3" t="n"/>
+      <c r="Z22" s="3" t="n"/>
+      <c r="AA22" s="3" t="n"/>
+      <c r="AB22" s="3" t="n"/>
+      <c r="AC22" s="3" t="n"/>
+      <c r="AD22" s="3" t="n"/>
+      <c r="AE22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n"/>
+      <c r="X23" s="3" t="n"/>
+      <c r="Y23" s="3" t="n"/>
+      <c r="Z23" s="3" t="n"/>
+      <c r="AA23" s="3" t="n"/>
+      <c r="AB23" s="3" t="n"/>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="3" t="n"/>
+      <c r="AE23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>■ 関連Apex/Flow/LWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="n"/>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="n"/>
+      <c r="W26" s="3" t="n"/>
+      <c r="X26" s="3" t="n"/>
+      <c r="Y26" s="3" t="n"/>
+      <c r="Z26" s="3" t="n"/>
+      <c r="AA26" s="3" t="n"/>
+      <c r="AB26" s="3" t="n"/>
+      <c r="AC26" s="3" t="n"/>
+      <c r="AD26" s="3" t="n"/>
+      <c r="AE26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="3" t="n"/>
+      <c r="U27" s="3" t="n"/>
+      <c r="V27" s="3" t="n"/>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="3" t="n"/>
+      <c r="Y27" s="3" t="n"/>
+      <c r="Z27" s="3" t="n"/>
+      <c r="AA27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" s="3" t="n"/>
+      <c r="AD27" s="3" t="n"/>
+      <c r="AE27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="3" t="n"/>
+      <c r="V28" s="3" t="n"/>
+      <c r="W28" s="3" t="n"/>
+      <c r="X28" s="3" t="n"/>
+      <c r="Y28" s="3" t="n"/>
+      <c r="Z28" s="3" t="n"/>
+      <c r="AA28" s="3" t="n"/>
+      <c r="AB28" s="3" t="n"/>
+      <c r="AC28" s="3" t="n"/>
+      <c r="AD28" s="3" t="n"/>
+      <c r="AE28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="3" t="n"/>
+      <c r="T29" s="3" t="n"/>
+      <c r="U29" s="3" t="n"/>
+      <c r="V29" s="3" t="n"/>
+      <c r="W29" s="3" t="n"/>
+      <c r="X29" s="3" t="n"/>
+      <c r="Y29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n"/>
+      <c r="AA29" s="3" t="n"/>
+      <c r="AB29" s="3" t="n"/>
+      <c r="AC29" s="3" t="n"/>
+      <c r="AD29" s="3" t="n"/>
+      <c r="AE29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="3" t="n"/>
+      <c r="U30" s="3" t="n"/>
+      <c r="V30" s="3" t="n"/>
+      <c r="W30" s="3" t="n"/>
+      <c r="X30" s="3" t="n"/>
+      <c r="Y30" s="3" t="n"/>
+      <c r="Z30" s="3" t="n"/>
+      <c r="AA30" s="3" t="n"/>
+      <c r="AB30" s="3" t="n"/>
+      <c r="AC30" s="3" t="n"/>
+      <c r="AD30" s="3" t="n"/>
+      <c r="AE30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
+      <c r="R31" s="3" t="n"/>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="n"/>
+      <c r="U31" s="3" t="n"/>
+      <c r="V31" s="3" t="n"/>
+      <c r="W31" s="3" t="n"/>
+      <c r="X31" s="3" t="n"/>
+      <c r="Y31" s="3" t="n"/>
+      <c r="Z31" s="3" t="n"/>
+      <c r="AA31" s="3" t="n"/>
+      <c r="AB31" s="3" t="n"/>
+      <c r="AC31" s="3" t="n"/>
+      <c r="AD31" s="3" t="n"/>
+      <c r="AE31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="3" t="n"/>
+      <c r="Q32" s="3" t="n"/>
+      <c r="R32" s="3" t="n"/>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n"/>
+      <c r="U32" s="3" t="n"/>
+      <c r="V32" s="3" t="n"/>
+      <c r="W32" s="3" t="n"/>
+      <c r="X32" s="3" t="n"/>
+      <c r="Y32" s="3" t="n"/>
+      <c r="Z32" s="3" t="n"/>
+      <c r="AA32" s="3" t="n"/>
+      <c r="AB32" s="3" t="n"/>
+      <c r="AC32" s="3" t="n"/>
+      <c r="AD32" s="3" t="n"/>
+      <c r="AE32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="3" t="n"/>
+      <c r="U33" s="3" t="n"/>
+      <c r="V33" s="3" t="n"/>
+      <c r="W33" s="3" t="n"/>
+      <c r="X33" s="3" t="n"/>
+      <c r="Y33" s="3" t="n"/>
+      <c r="Z33" s="3" t="n"/>
+      <c r="AA33" s="3" t="n"/>
+      <c r="AB33" s="3" t="n"/>
+      <c r="AC33" s="3" t="n"/>
+      <c r="AD33" s="3" t="n"/>
+      <c r="AE33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n"/>
+      <c r="Q34" s="3" t="n"/>
+      <c r="R34" s="3" t="n"/>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="3" t="n"/>
+      <c r="U34" s="3" t="n"/>
+      <c r="V34" s="3" t="n"/>
+      <c r="W34" s="3" t="n"/>
+      <c r="X34" s="3" t="n"/>
+      <c r="Y34" s="3" t="n"/>
+      <c r="Z34" s="3" t="n"/>
+      <c r="AA34" s="3" t="n"/>
+      <c r="AB34" s="3" t="n"/>
+      <c r="AC34" s="3" t="n"/>
+      <c r="AD34" s="3" t="n"/>
+      <c r="AE34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="6" customHeight="1"/>
+    <row r="36" ht="26" customHeight="1">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>■ 外部連携影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>連携先</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>影響内容</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n"/>
+      <c r="Q37" s="3" t="n"/>
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" s="3" t="n"/>
+      <c r="T37" s="3" t="n"/>
+      <c r="U37" s="3" t="n"/>
+      <c r="V37" s="3" t="n"/>
+      <c r="W37" s="3" t="n"/>
+      <c r="X37" s="3" t="n"/>
+      <c r="Y37" s="3" t="n"/>
+      <c r="Z37" s="3" t="n"/>
+      <c r="AA37" s="3" t="n"/>
+      <c r="AB37" s="3" t="n"/>
+      <c r="AC37" s="3" t="n"/>
+      <c r="AD37" s="3" t="n"/>
+      <c r="AE37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
+      <c r="O38" s="3" t="n"/>
+      <c r="P38" s="3" t="n"/>
+      <c r="Q38" s="3" t="n"/>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="n"/>
+      <c r="T38" s="3" t="n"/>
+      <c r="U38" s="3" t="n"/>
+      <c r="V38" s="3" t="n"/>
+      <c r="W38" s="3" t="n"/>
+      <c r="X38" s="3" t="n"/>
+      <c r="Y38" s="3" t="n"/>
+      <c r="Z38" s="3" t="n"/>
+      <c r="AA38" s="3" t="n"/>
+      <c r="AB38" s="3" t="n"/>
+      <c r="AC38" s="3" t="n"/>
+      <c r="AD38" s="3" t="n"/>
+      <c r="AE38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="3" t="n"/>
+      <c r="U39" s="3" t="n"/>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" s="3" t="n"/>
+      <c r="X39" s="3" t="n"/>
+      <c r="Y39" s="3" t="n"/>
+      <c r="Z39" s="3" t="n"/>
+      <c r="AA39" s="3" t="n"/>
+      <c r="AB39" s="3" t="n"/>
+      <c r="AC39" s="3" t="n"/>
+      <c r="AD39" s="3" t="n"/>
+      <c r="AE39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3" t="n"/>
+      <c r="O40" s="3" t="n"/>
+      <c r="P40" s="3" t="n"/>
+      <c r="Q40" s="3" t="n"/>
+      <c r="R40" s="3" t="n"/>
+      <c r="S40" s="3" t="n"/>
+      <c r="T40" s="3" t="n"/>
+      <c r="U40" s="3" t="n"/>
+      <c r="V40" s="3" t="n"/>
+      <c r="W40" s="3" t="n"/>
+      <c r="X40" s="3" t="n"/>
+      <c r="Y40" s="3" t="n"/>
+      <c r="Z40" s="3" t="n"/>
+      <c r="AA40" s="3" t="n"/>
+      <c r="AB40" s="3" t="n"/>
+      <c r="AC40" s="3" t="n"/>
+      <c r="AD40" s="3" t="n"/>
+      <c r="AE40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
+      <c r="Q41" s="3" t="n"/>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="n"/>
+      <c r="T41" s="3" t="n"/>
+      <c r="U41" s="3" t="n"/>
+      <c r="V41" s="3" t="n"/>
+      <c r="W41" s="3" t="n"/>
+      <c r="X41" s="3" t="n"/>
+      <c r="Y41" s="3" t="n"/>
+      <c r="Z41" s="3" t="n"/>
+      <c r="AA41" s="3" t="n"/>
+      <c r="AB41" s="3" t="n"/>
+      <c r="AC41" s="3" t="n"/>
+      <c r="AD41" s="3" t="n"/>
+      <c r="AE41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
+      <c r="N42" s="3" t="n"/>
+      <c r="O42" s="3" t="n"/>
+      <c r="P42" s="3" t="n"/>
+      <c r="Q42" s="3" t="n"/>
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" s="3" t="n"/>
+      <c r="T42" s="3" t="n"/>
+      <c r="U42" s="3" t="n"/>
+      <c r="V42" s="3" t="n"/>
+      <c r="W42" s="3" t="n"/>
+      <c r="X42" s="3" t="n"/>
+      <c r="Y42" s="3" t="n"/>
+      <c r="Z42" s="3" t="n"/>
+      <c r="AA42" s="3" t="n"/>
+      <c r="AB42" s="3" t="n"/>
+      <c r="AC42" s="3" t="n"/>
+      <c r="AD42" s="3" t="n"/>
+      <c r="AE42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>■ 他機能依存</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>機能名</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>依存内容</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n"/>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
+      <c r="T45" s="3" t="n"/>
+      <c r="U45" s="3" t="n"/>
+      <c r="V45" s="3" t="n"/>
+      <c r="W45" s="3" t="n"/>
+      <c r="X45" s="3" t="n"/>
+      <c r="Y45" s="3" t="n"/>
+      <c r="Z45" s="3" t="n"/>
+      <c r="AA45" s="3" t="n"/>
+      <c r="AB45" s="3" t="n"/>
+      <c r="AC45" s="3" t="n"/>
+      <c r="AD45" s="3" t="n"/>
+      <c r="AE45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="3" t="n"/>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="3" t="n"/>
+      <c r="V46" s="3" t="n"/>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
+      <c r="Z46" s="3" t="n"/>
+      <c r="AA46" s="3" t="n"/>
+      <c r="AB46" s="3" t="n"/>
+      <c r="AC46" s="3" t="n"/>
+      <c r="AD46" s="3" t="n"/>
+      <c r="AE46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="5" t="inlineStr"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="3" t="n"/>
+      <c r="Q47" s="3" t="n"/>
+      <c r="R47" s="3" t="n"/>
+      <c r="S47" s="3" t="n"/>
+      <c r="T47" s="3" t="n"/>
+      <c r="U47" s="3" t="n"/>
+      <c r="V47" s="3" t="n"/>
+      <c r="W47" s="3" t="n"/>
+      <c r="X47" s="3" t="n"/>
+      <c r="Y47" s="3" t="n"/>
+      <c r="Z47" s="3" t="n"/>
+      <c r="AA47" s="3" t="n"/>
+      <c r="AB47" s="3" t="n"/>
+      <c r="AC47" s="3" t="n"/>
+      <c r="AD47" s="3" t="n"/>
+      <c r="AE47" s="4" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="5" t="inlineStr"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="3" t="n"/>
+      <c r="Q48" s="3" t="n"/>
+      <c r="R48" s="3" t="n"/>
+      <c r="S48" s="3" t="n"/>
+      <c r="T48" s="3" t="n"/>
+      <c r="U48" s="3" t="n"/>
+      <c r="V48" s="3" t="n"/>
+      <c r="W48" s="3" t="n"/>
+      <c r="X48" s="3" t="n"/>
+      <c r="Y48" s="3" t="n"/>
+      <c r="Z48" s="3" t="n"/>
+      <c r="AA48" s="3" t="n"/>
+      <c r="AB48" s="3" t="n"/>
+      <c r="AC48" s="3" t="n"/>
+      <c r="AD48" s="3" t="n"/>
+      <c r="AE48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
+      <c r="N49" s="3" t="n"/>
+      <c r="O49" s="3" t="n"/>
+      <c r="P49" s="3" t="n"/>
+      <c r="Q49" s="3" t="n"/>
+      <c r="R49" s="3" t="n"/>
+      <c r="S49" s="3" t="n"/>
+      <c r="T49" s="3" t="n"/>
+      <c r="U49" s="3" t="n"/>
+      <c r="V49" s="3" t="n"/>
+      <c r="W49" s="3" t="n"/>
+      <c r="X49" s="3" t="n"/>
+      <c r="Y49" s="3" t="n"/>
+      <c r="Z49" s="3" t="n"/>
+      <c r="AA49" s="3" t="n"/>
+      <c r="AB49" s="3" t="n"/>
+      <c r="AC49" s="3" t="n"/>
+      <c r="AD49" s="3" t="n"/>
+      <c r="AE49" s="4" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="5" t="inlineStr"/>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="3" t="n"/>
+      <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="n"/>
+      <c r="N50" s="3" t="n"/>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="3" t="n"/>
+      <c r="Q50" s="3" t="n"/>
+      <c r="R50" s="3" t="n"/>
+      <c r="S50" s="3" t="n"/>
+      <c r="T50" s="3" t="n"/>
+      <c r="U50" s="3" t="n"/>
+      <c r="V50" s="3" t="n"/>
+      <c r="W50" s="3" t="n"/>
+      <c r="X50" s="3" t="n"/>
+      <c r="Y50" s="3" t="n"/>
+      <c r="Z50" s="3" t="n"/>
+      <c r="AA50" s="3" t="n"/>
+      <c r="AB50" s="3" t="n"/>
+      <c r="AC50" s="3" t="n"/>
+      <c r="AD50" s="3" t="n"/>
+      <c r="AE50" s="4" t="n"/>
+    </row>
+    <row r="51" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="130">
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="Y18:AE18"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="V12:X12"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="Y13:AE13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="Y8:AE8"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="Y9:AE9"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="Y14:AE14"/>
-    <mergeCell ref="Y11:AE11"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="V5:X5"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="Y6:AE6"/>
-    <mergeCell ref="I7:N7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="Y5:AE5"/>
-    <mergeCell ref="Y19:AE19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="I11:N11"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="Y17:AE17"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="V19:X19"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="Y12:AE12"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="V6:X6"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V11:X11"/>
+  <mergeCells count="111">
+    <mergeCell ref="J17:T17"/>
+    <mergeCell ref="J41:AE41"/>
+    <mergeCell ref="U15:AE15"/>
+    <mergeCell ref="J5:T5"/>
+    <mergeCell ref="J19:T19"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J9:T9"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="J42:AE42"/>
+    <mergeCell ref="U16:AE16"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J4:T4"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="J37:AE37"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N26:AE26"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="U5:AE5"/>
+    <mergeCell ref="U20:AE20"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="J18:T18"/>
+    <mergeCell ref="U4:AE4"/>
+    <mergeCell ref="J8:T8"/>
+    <mergeCell ref="U22:AE22"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="U6:AE6"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="J47:AE47"/>
+    <mergeCell ref="J10:T10"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B44:AE44"/>
+    <mergeCell ref="N29:AE29"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="N31:AE31"/>
+    <mergeCell ref="J11:T11"/>
+    <mergeCell ref="J20:T20"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="U18:AE18"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="J22:T22"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="U8:AE8"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="J49:AE49"/>
+    <mergeCell ref="J12:T12"/>
+    <mergeCell ref="N32:AE32"/>
+    <mergeCell ref="J21:T21"/>
+    <mergeCell ref="J45:AE45"/>
+    <mergeCell ref="U10:AE10"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="U19:AE19"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="J23:T23"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="U9:AE9"/>
+    <mergeCell ref="N33:AE33"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="N28:AE28"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="U7:AE7"/>
+    <mergeCell ref="N30:AE30"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="U21:AE21"/>
+    <mergeCell ref="J16:T16"/>
+    <mergeCell ref="B36:AE36"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B14:AE14"/>
+    <mergeCell ref="J50:AE50"/>
+    <mergeCell ref="B18:I18"/>
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="Y15:AE15"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="Y10:AE10"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="J46:AE46"/>
+    <mergeCell ref="U17:AE17"/>
+    <mergeCell ref="J6:T6"/>
+    <mergeCell ref="U11:AE11"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="J15:T15"/>
+    <mergeCell ref="J39:AE39"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J48:AE48"/>
+    <mergeCell ref="N34:AE34"/>
+    <mergeCell ref="J38:AE38"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="U12:AE12"/>
+    <mergeCell ref="J7:T7"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="N27:AE27"/>
+    <mergeCell ref="J40:AE40"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B25:AE25"/>
     <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="Y7:AE7"/>
-    <mergeCell ref="Y16:AE16"/>
+    <mergeCell ref="U23:AE23"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
@@ -61,7 +61,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -88,13 +88,8 @@
         <fgColor rgb="000070C0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,60 +155,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="008B9DC3"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="008B9DC3"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="008B9DC3"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="008B9DC3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="008B9DC3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="008B9DC3"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="008B9DC3"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,14 +178,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2613,182 +2551,36 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
-      <c r="O27" s="9" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="9" t="n"/>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="9" t="n"/>
-      <c r="U27" s="9" t="n"/>
-      <c r="V27" s="9" t="n"/>
-      <c r="W27" s="9" t="n"/>
-      <c r="X27" s="9" t="n"/>
-      <c r="Y27" s="9" t="n"/>
-      <c r="Z27" s="9" t="n"/>
-      <c r="AA27" s="9" t="n"/>
-      <c r="AB27" s="9" t="n"/>
-      <c r="AC27" s="9" t="n"/>
-      <c r="AD27" s="9" t="n"/>
-      <c r="AE27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="11" t="n"/>
-      <c r="AE28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="11" t="n"/>
-      <c r="AE29" s="12" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="11" t="n"/>
-      <c r="AE30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="11" t="n"/>
-      <c r="AE31" s="12" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="11" t="n"/>
-      <c r="AE32" s="12" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="11" t="n"/>
-      <c r="AE33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="B34" s="11" t="n"/>
-      <c r="AE34" s="12" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="11" t="n"/>
-      <c r="AE35" s="12" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="B36" s="11" t="n"/>
-      <c r="AE36" s="12" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="11" t="n"/>
-      <c r="AE37" s="12" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="11" t="n"/>
-      <c r="AE38" s="12" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="11" t="n"/>
-      <c r="AE39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="11" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="B41" s="11" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="B42" s="11" t="n"/>
-      <c r="AE42" s="12" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="n"/>
-      <c r="AE43" s="12" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="11" t="n"/>
-      <c r="AE44" s="12" t="n"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="B45" s="11" t="n"/>
-      <c r="AE45" s="12" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="B46" s="11" t="n"/>
-      <c r="AE46" s="12" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="11" t="n"/>
-      <c r="AE47" s="12" t="n"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="B48" s="11" t="n"/>
-      <c r="AE48" s="12" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="11" t="n"/>
-      <c r="AE49" s="12" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="11" t="n"/>
-      <c r="AE50" s="12" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="B51" s="11" t="n"/>
-      <c r="AE51" s="12" t="n"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="B52" s="11" t="n"/>
-      <c r="AE52" s="12" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="B53" s="11" t="n"/>
-      <c r="AE53" s="12" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="B54" s="11" t="n"/>
-      <c r="AE54" s="12" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="B55" s="11" t="n"/>
-      <c r="AE55" s="12" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="14" t="n"/>
-      <c r="D56" s="14" t="n"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="14" t="n"/>
-      <c r="G56" s="14" t="n"/>
-      <c r="H56" s="14" t="n"/>
-      <c r="I56" s="14" t="n"/>
-      <c r="J56" s="14" t="n"/>
-      <c r="K56" s="14" t="n"/>
-      <c r="L56" s="14" t="n"/>
-      <c r="M56" s="14" t="n"/>
-      <c r="N56" s="14" t="n"/>
-      <c r="O56" s="14" t="n"/>
-      <c r="P56" s="14" t="n"/>
-      <c r="Q56" s="14" t="n"/>
-      <c r="R56" s="14" t="n"/>
-      <c r="S56" s="14" t="n"/>
-      <c r="T56" s="14" t="n"/>
-      <c r="U56" s="14" t="n"/>
-      <c r="V56" s="14" t="n"/>
-      <c r="W56" s="14" t="n"/>
-      <c r="X56" s="14" t="n"/>
-      <c r="Y56" s="14" t="n"/>
-      <c r="Z56" s="14" t="n"/>
-      <c r="AA56" s="14" t="n"/>
-      <c r="AB56" s="14" t="n"/>
-      <c r="AC56" s="14" t="n"/>
-      <c r="AD56" s="14" t="n"/>
-      <c r="AE56" s="15" t="n"/>
-    </row>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="20" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1"/>
     <row r="57" ht="8" customHeight="1"/>
   </sheetData>
   <mergeCells count="88">
@@ -3962,182 +3754,36 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="9" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="9" t="n"/>
-      <c r="O37" s="9" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
-      <c r="T37" s="9" t="n"/>
-      <c r="U37" s="9" t="n"/>
-      <c r="V37" s="9" t="n"/>
-      <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
-      <c r="Y37" s="9" t="n"/>
-      <c r="Z37" s="9" t="n"/>
-      <c r="AA37" s="9" t="n"/>
-      <c r="AB37" s="9" t="n"/>
-      <c r="AC37" s="9" t="n"/>
-      <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="11" t="n"/>
-      <c r="AE38" s="12" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="11" t="n"/>
-      <c r="AE39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="11" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="B41" s="11" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="B42" s="11" t="n"/>
-      <c r="AE42" s="12" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="n"/>
-      <c r="AE43" s="12" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="11" t="n"/>
-      <c r="AE44" s="12" t="n"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="B45" s="11" t="n"/>
-      <c r="AE45" s="12" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="B46" s="11" t="n"/>
-      <c r="AE46" s="12" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="11" t="n"/>
-      <c r="AE47" s="12" t="n"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="B48" s="11" t="n"/>
-      <c r="AE48" s="12" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="11" t="n"/>
-      <c r="AE49" s="12" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="11" t="n"/>
-      <c r="AE50" s="12" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="B51" s="11" t="n"/>
-      <c r="AE51" s="12" t="n"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="B52" s="11" t="n"/>
-      <c r="AE52" s="12" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="B53" s="11" t="n"/>
-      <c r="AE53" s="12" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="B54" s="11" t="n"/>
-      <c r="AE54" s="12" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="B55" s="11" t="n"/>
-      <c r="AE55" s="12" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="B56" s="11" t="n"/>
-      <c r="AE56" s="12" t="n"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="B57" s="11" t="n"/>
-      <c r="AE57" s="12" t="n"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="B58" s="11" t="n"/>
-      <c r="AE58" s="12" t="n"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="B59" s="11" t="n"/>
-      <c r="AE59" s="12" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="B60" s="11" t="n"/>
-      <c r="AE60" s="12" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="B61" s="11" t="n"/>
-      <c r="AE61" s="12" t="n"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="B62" s="11" t="n"/>
-      <c r="AE62" s="12" t="n"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="B63" s="11" t="n"/>
-      <c r="AE63" s="12" t="n"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="B64" s="11" t="n"/>
-      <c r="AE64" s="12" t="n"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="B65" s="11" t="n"/>
-      <c r="AE65" s="12" t="n"/>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="B66" s="13" t="n"/>
-      <c r="C66" s="14" t="n"/>
-      <c r="D66" s="14" t="n"/>
-      <c r="E66" s="14" t="n"/>
-      <c r="F66" s="14" t="n"/>
-      <c r="G66" s="14" t="n"/>
-      <c r="H66" s="14" t="n"/>
-      <c r="I66" s="14" t="n"/>
-      <c r="J66" s="14" t="n"/>
-      <c r="K66" s="14" t="n"/>
-      <c r="L66" s="14" t="n"/>
-      <c r="M66" s="14" t="n"/>
-      <c r="N66" s="14" t="n"/>
-      <c r="O66" s="14" t="n"/>
-      <c r="P66" s="14" t="n"/>
-      <c r="Q66" s="14" t="n"/>
-      <c r="R66" s="14" t="n"/>
-      <c r="S66" s="14" t="n"/>
-      <c r="T66" s="14" t="n"/>
-      <c r="U66" s="14" t="n"/>
-      <c r="V66" s="14" t="n"/>
-      <c r="W66" s="14" t="n"/>
-      <c r="X66" s="14" t="n"/>
-      <c r="Y66" s="14" t="n"/>
-      <c r="Z66" s="14" t="n"/>
-      <c r="AA66" s="14" t="n"/>
-      <c r="AB66" s="14" t="n"/>
-      <c r="AC66" s="14" t="n"/>
-      <c r="AD66" s="14" t="n"/>
-      <c r="AE66" s="15" t="n"/>
-    </row>
+    <row r="37" ht="20" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1"/>
+    <row r="61" ht="20" customHeight="1"/>
+    <row r="62" ht="20" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1"/>
+    <row r="64" ht="20" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1"/>
+    <row r="66" ht="20" customHeight="1"/>
     <row r="67" ht="8" customHeight="1"/>
   </sheetData>
   <mergeCells count="159">
@@ -4365,7 +4011,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>ステップNo</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -4382,32 +4028,28 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>条件分岐</t>
+          <t>コンポーネント</t>
         </is>
       </c>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>SOQL概要</t>
+          <t>分岐条件</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="6" t="inlineStr">
-        <is>
-          <t>DML操作</t>
-        </is>
-      </c>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="n"/>
       <c r="AB4" s="3" t="n"/>
       <c r="AC4" s="3" t="n"/>
@@ -4426,20 +4068,20 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="5" t="inlineStr"/>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
-      <c r="S5" s="4" t="n"/>
-      <c r="T5" s="5" t="inlineStr"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="3" t="n"/>
-      <c r="W5" s="3" t="n"/>
+      <c r="V5" s="4" t="n"/>
+      <c r="W5" s="5" t="inlineStr"/>
       <c r="X5" s="3" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="n"/>
       <c r="AB5" s="3" t="n"/>
       <c r="AC5" s="3" t="n"/>
@@ -4458,20 +4100,20 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="3" t="n"/>
       <c r="R6" s="3" t="n"/>
-      <c r="S6" s="4" t="n"/>
-      <c r="T6" s="5" t="inlineStr"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
+      <c r="V6" s="4" t="n"/>
+      <c r="W6" s="5" t="inlineStr"/>
       <c r="X6" s="3" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
       <c r="AA6" s="3" t="n"/>
       <c r="AB6" s="3" t="n"/>
       <c r="AC6" s="3" t="n"/>
@@ -4490,20 +4132,20 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
-      <c r="S7" s="4" t="n"/>
-      <c r="T7" s="5" t="inlineStr"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
+      <c r="V7" s="4" t="n"/>
+      <c r="W7" s="5" t="inlineStr"/>
       <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="Y7" s="3" t="n"/>
+      <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="n"/>
       <c r="AB7" s="3" t="n"/>
       <c r="AC7" s="3" t="n"/>
@@ -4522,20 +4164,20 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="5" t="inlineStr"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
-      <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
+      <c r="V8" s="4" t="n"/>
+      <c r="W8" s="5" t="inlineStr"/>
       <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="Y8" s="3" t="n"/>
+      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="n"/>
       <c r="AB8" s="3" t="n"/>
       <c r="AC8" s="3" t="n"/>
@@ -4554,20 +4196,20 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="3" t="n"/>
       <c r="R9" s="3" t="n"/>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="5" t="inlineStr"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
+      <c r="V9" s="4" t="n"/>
+      <c r="W9" s="5" t="inlineStr"/>
       <c r="X9" s="3" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="Y9" s="3" t="n"/>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="n"/>
       <c r="AB9" s="3" t="n"/>
       <c r="AC9" s="3" t="n"/>
@@ -4586,20 +4228,20 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="5" t="inlineStr"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
+      <c r="V10" s="4" t="n"/>
+      <c r="W10" s="5" t="inlineStr"/>
       <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="n"/>
       <c r="AB10" s="3" t="n"/>
       <c r="AC10" s="3" t="n"/>
@@ -4618,20 +4260,20 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="5" t="inlineStr"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
+      <c r="V11" s="4" t="n"/>
+      <c r="W11" s="5" t="inlineStr"/>
       <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="n"/>
       <c r="AB11" s="3" t="n"/>
       <c r="AC11" s="3" t="n"/>
@@ -4650,20 +4292,20 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="5" t="inlineStr"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="3" t="n"/>
       <c r="R12" s="3" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="5" t="inlineStr"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n"/>
       <c r="U12" s="3" t="n"/>
-      <c r="V12" s="3" t="n"/>
-      <c r="W12" s="3" t="n"/>
+      <c r="V12" s="4" t="n"/>
+      <c r="W12" s="5" t="inlineStr"/>
       <c r="X12" s="3" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="5" t="inlineStr"/>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="n"/>
       <c r="AB12" s="3" t="n"/>
       <c r="AC12" s="3" t="n"/>
@@ -4682,20 +4324,20 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="3" t="n"/>
       <c r="R13" s="3" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="5" t="inlineStr"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
       <c r="U13" s="3" t="n"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
+      <c r="V13" s="4" t="n"/>
+      <c r="W13" s="5" t="inlineStr"/>
       <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="5" t="inlineStr"/>
+      <c r="Y13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="n"/>
       <c r="AB13" s="3" t="n"/>
       <c r="AC13" s="3" t="n"/>
@@ -4714,20 +4356,20 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="3" t="n"/>
       <c r="R14" s="3" t="n"/>
-      <c r="S14" s="4" t="n"/>
-      <c r="T14" s="5" t="inlineStr"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
+      <c r="V14" s="4" t="n"/>
+      <c r="W14" s="5" t="inlineStr"/>
       <c r="X14" s="3" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="Y14" s="3" t="n"/>
+      <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="n"/>
       <c r="AB14" s="3" t="n"/>
       <c r="AC14" s="3" t="n"/>
@@ -4746,20 +4388,20 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="5" t="inlineStr"/>
       <c r="Q15" s="3" t="n"/>
       <c r="R15" s="3" t="n"/>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="5" t="inlineStr"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
+      <c r="V15" s="4" t="n"/>
+      <c r="W15" s="5" t="inlineStr"/>
       <c r="X15" s="3" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="5" t="inlineStr"/>
+      <c r="Y15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="n"/>
       <c r="AB15" s="3" t="n"/>
       <c r="AC15" s="3" t="n"/>
@@ -4778,20 +4420,20 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="5" t="inlineStr"/>
       <c r="Q16" s="3" t="n"/>
       <c r="R16" s="3" t="n"/>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="5" t="inlineStr"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
       <c r="U16" s="3" t="n"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
+      <c r="V16" s="4" t="n"/>
+      <c r="W16" s="5" t="inlineStr"/>
       <c r="X16" s="3" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="5" t="inlineStr"/>
+      <c r="Y16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="n"/>
       <c r="AB16" s="3" t="n"/>
       <c r="AC16" s="3" t="n"/>
@@ -4810,20 +4452,20 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="5" t="inlineStr"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="3" t="n"/>
       <c r="R17" s="3" t="n"/>
-      <c r="S17" s="4" t="n"/>
-      <c r="T17" s="5" t="inlineStr"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="n"/>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="3" t="n"/>
+      <c r="V17" s="4" t="n"/>
+      <c r="W17" s="5" t="inlineStr"/>
       <c r="X17" s="3" t="n"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="5" t="inlineStr"/>
+      <c r="Y17" s="3" t="n"/>
+      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="n"/>
       <c r="AB17" s="3" t="n"/>
       <c r="AC17" s="3" t="n"/>
@@ -4842,20 +4484,20 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="5" t="inlineStr"/>
       <c r="Q18" s="3" t="n"/>
       <c r="R18" s="3" t="n"/>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="5" t="inlineStr"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="3" t="n"/>
       <c r="U18" s="3" t="n"/>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n"/>
+      <c r="V18" s="4" t="n"/>
+      <c r="W18" s="5" t="inlineStr"/>
       <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="5" t="inlineStr"/>
+      <c r="Y18" s="3" t="n"/>
+      <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="n"/>
       <c r="AB18" s="3" t="n"/>
       <c r="AC18" s="3" t="n"/>
@@ -4874,20 +4516,20 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="5" t="inlineStr"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="5" t="inlineStr"/>
       <c r="Q19" s="3" t="n"/>
       <c r="R19" s="3" t="n"/>
-      <c r="S19" s="4" t="n"/>
-      <c r="T19" s="5" t="inlineStr"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="n"/>
-      <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
+      <c r="V19" s="4" t="n"/>
+      <c r="W19" s="5" t="inlineStr"/>
       <c r="X19" s="3" t="n"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="5" t="inlineStr"/>
+      <c r="Y19" s="3" t="n"/>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="n"/>
       <c r="AB19" s="3" t="n"/>
       <c r="AC19" s="3" t="n"/>
@@ -4906,20 +4548,20 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="5" t="inlineStr"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="P20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="5" t="inlineStr"/>
       <c r="Q20" s="3" t="n"/>
       <c r="R20" s="3" t="n"/>
-      <c r="S20" s="4" t="n"/>
-      <c r="T20" s="5" t="inlineStr"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="3" t="n"/>
       <c r="U20" s="3" t="n"/>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
+      <c r="V20" s="4" t="n"/>
+      <c r="W20" s="5" t="inlineStr"/>
       <c r="X20" s="3" t="n"/>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="Y20" s="3" t="n"/>
+      <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="n"/>
       <c r="AB20" s="3" t="n"/>
       <c r="AC20" s="3" t="n"/>
@@ -4938,20 +4580,20 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="n"/>
-      <c r="S21" s="4" t="n"/>
-      <c r="T21" s="5" t="inlineStr"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n"/>
-      <c r="W21" s="3" t="n"/>
+      <c r="V21" s="4" t="n"/>
+      <c r="W21" s="5" t="inlineStr"/>
       <c r="X21" s="3" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="n"/>
       <c r="AB21" s="3" t="n"/>
       <c r="AC21" s="3" t="n"/>
@@ -4970,20 +4612,20 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="3" t="n"/>
-      <c r="P22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="5" t="inlineStr"/>
       <c r="Q22" s="3" t="n"/>
       <c r="R22" s="3" t="n"/>
-      <c r="S22" s="4" t="n"/>
-      <c r="T22" s="5" t="inlineStr"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
       <c r="U22" s="3" t="n"/>
-      <c r="V22" s="3" t="n"/>
-      <c r="W22" s="3" t="n"/>
+      <c r="V22" s="4" t="n"/>
+      <c r="W22" s="5" t="inlineStr"/>
       <c r="X22" s="3" t="n"/>
-      <c r="Y22" s="4" t="n"/>
-      <c r="Z22" s="5" t="inlineStr"/>
+      <c r="Y22" s="3" t="n"/>
+      <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="n"/>
       <c r="AB22" s="3" t="n"/>
       <c r="AC22" s="3" t="n"/>
@@ -5002,20 +4644,20 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="5" t="inlineStr"/>
       <c r="Q23" s="3" t="n"/>
       <c r="R23" s="3" t="n"/>
-      <c r="S23" s="4" t="n"/>
-      <c r="T23" s="5" t="inlineStr"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n"/>
       <c r="U23" s="3" t="n"/>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
+      <c r="V23" s="4" t="n"/>
+      <c r="W23" s="5" t="inlineStr"/>
       <c r="X23" s="3" t="n"/>
-      <c r="Y23" s="4" t="n"/>
-      <c r="Z23" s="5" t="inlineStr"/>
+      <c r="Y23" s="3" t="n"/>
+      <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="n"/>
       <c r="AB23" s="3" t="n"/>
       <c r="AC23" s="3" t="n"/>
@@ -5034,20 +4676,20 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="5" t="inlineStr"/>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n"/>
-      <c r="S24" s="4" t="n"/>
-      <c r="T24" s="5" t="inlineStr"/>
+      <c r="S24" s="3" t="n"/>
+      <c r="T24" s="3" t="n"/>
       <c r="U24" s="3" t="n"/>
-      <c r="V24" s="3" t="n"/>
-      <c r="W24" s="3" t="n"/>
+      <c r="V24" s="4" t="n"/>
+      <c r="W24" s="5" t="inlineStr"/>
       <c r="X24" s="3" t="n"/>
-      <c r="Y24" s="4" t="n"/>
-      <c r="Z24" s="5" t="inlineStr"/>
+      <c r="Y24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="n"/>
       <c r="AB24" s="3" t="n"/>
       <c r="AC24" s="3" t="n"/>
@@ -5062,294 +4704,127 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
-      <c r="O27" s="9" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="9" t="n"/>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="9" t="n"/>
-      <c r="U27" s="9" t="n"/>
-      <c r="V27" s="9" t="n"/>
-      <c r="W27" s="9" t="n"/>
-      <c r="X27" s="9" t="n"/>
-      <c r="Y27" s="9" t="n"/>
-      <c r="Z27" s="9" t="n"/>
-      <c r="AA27" s="9" t="n"/>
-      <c r="AB27" s="9" t="n"/>
-      <c r="AC27" s="9" t="n"/>
-      <c r="AD27" s="9" t="n"/>
-      <c r="AE27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="11" t="n"/>
-      <c r="AE28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="11" t="n"/>
-      <c r="AE29" s="12" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="11" t="n"/>
-      <c r="AE30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="11" t="n"/>
-      <c r="AE31" s="12" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="11" t="n"/>
-      <c r="AE32" s="12" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="11" t="n"/>
-      <c r="AE33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="B34" s="11" t="n"/>
-      <c r="AE34" s="12" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="11" t="n"/>
-      <c r="AE35" s="12" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="B36" s="11" t="n"/>
-      <c r="AE36" s="12" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="11" t="n"/>
-      <c r="AE37" s="12" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="11" t="n"/>
-      <c r="AE38" s="12" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="11" t="n"/>
-      <c r="AE39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="11" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="B41" s="11" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="B42" s="11" t="n"/>
-      <c r="AE42" s="12" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="n"/>
-      <c r="AE43" s="12" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="11" t="n"/>
-      <c r="AE44" s="12" t="n"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="B45" s="11" t="n"/>
-      <c r="AE45" s="12" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="B46" s="11" t="n"/>
-      <c r="AE46" s="12" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="11" t="n"/>
-      <c r="AE47" s="12" t="n"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="B48" s="11" t="n"/>
-      <c r="AE48" s="12" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="11" t="n"/>
-      <c r="AE49" s="12" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="11" t="n"/>
-      <c r="AE50" s="12" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="B51" s="11" t="n"/>
-      <c r="AE51" s="12" t="n"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="B52" s="11" t="n"/>
-      <c r="AE52" s="12" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="B53" s="11" t="n"/>
-      <c r="AE53" s="12" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="B54" s="11" t="n"/>
-      <c r="AE54" s="12" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="B55" s="11" t="n"/>
-      <c r="AE55" s="12" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="14" t="n"/>
-      <c r="D56" s="14" t="n"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="14" t="n"/>
-      <c r="G56" s="14" t="n"/>
-      <c r="H56" s="14" t="n"/>
-      <c r="I56" s="14" t="n"/>
-      <c r="J56" s="14" t="n"/>
-      <c r="K56" s="14" t="n"/>
-      <c r="L56" s="14" t="n"/>
-      <c r="M56" s="14" t="n"/>
-      <c r="N56" s="14" t="n"/>
-      <c r="O56" s="14" t="n"/>
-      <c r="P56" s="14" t="n"/>
-      <c r="Q56" s="14" t="n"/>
-      <c r="R56" s="14" t="n"/>
-      <c r="S56" s="14" t="n"/>
-      <c r="T56" s="14" t="n"/>
-      <c r="U56" s="14" t="n"/>
-      <c r="V56" s="14" t="n"/>
-      <c r="W56" s="14" t="n"/>
-      <c r="X56" s="14" t="n"/>
-      <c r="Y56" s="14" t="n"/>
-      <c r="Z56" s="14" t="n"/>
-      <c r="AA56" s="14" t="n"/>
-      <c r="AB56" s="14" t="n"/>
-      <c r="AC56" s="14" t="n"/>
-      <c r="AD56" s="14" t="n"/>
-      <c r="AE56" s="15" t="n"/>
-    </row>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="20" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1"/>
     <row r="57" ht="8" customHeight="1"/>
   </sheetData>
-  <mergeCells count="109">
-    <mergeCell ref="Z7:AE7"/>
-    <mergeCell ref="D12:M12"/>
-    <mergeCell ref="D9:M9"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N18:S18"/>
+  <mergeCells count="88">
+    <mergeCell ref="P13:V13"/>
+    <mergeCell ref="D11:O11"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="D14:M14"/>
+    <mergeCell ref="P15:V15"/>
+    <mergeCell ref="P24:V24"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D23:M23"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="T8:Y8"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="T16:Y16"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P10:V10"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="Z10:AE10"/>
-    <mergeCell ref="Z19:AE19"/>
-    <mergeCell ref="T18:Y18"/>
-    <mergeCell ref="Z9:AE9"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="N20:S20"/>
+    <mergeCell ref="D15:O15"/>
+    <mergeCell ref="D23:O23"/>
+    <mergeCell ref="P9:V9"/>
+    <mergeCell ref="W14:AE14"/>
+    <mergeCell ref="P11:V11"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="Z11:AE11"/>
-    <mergeCell ref="D17:M17"/>
-    <mergeCell ref="N22:S22"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="W6:AE6"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="N5:S5"/>
-    <mergeCell ref="N14:S14"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="T12:Y12"/>
+    <mergeCell ref="P12:V12"/>
+    <mergeCell ref="D17:O17"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="T21:Y21"/>
-    <mergeCell ref="D5:M5"/>
+    <mergeCell ref="W7:AE7"/>
+    <mergeCell ref="W16:AE16"/>
+    <mergeCell ref="P14:V14"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="Z23:AE23"/>
-    <mergeCell ref="T23:Y23"/>
-    <mergeCell ref="Z13:AE13"/>
-    <mergeCell ref="T13:Y13"/>
-    <mergeCell ref="T7:Y7"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="Z15:AE15"/>
-    <mergeCell ref="Z24:AE24"/>
-    <mergeCell ref="D21:M21"/>
+    <mergeCell ref="P4:V4"/>
+    <mergeCell ref="W18:AE18"/>
+    <mergeCell ref="D12:O12"/>
+    <mergeCell ref="W8:AE8"/>
+    <mergeCell ref="W17:AE17"/>
+    <mergeCell ref="W11:AE11"/>
+    <mergeCell ref="D5:O5"/>
+    <mergeCell ref="D14:O14"/>
+    <mergeCell ref="W19:AE19"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="N16:S16"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D7:M7"/>
-    <mergeCell ref="D16:M16"/>
+    <mergeCell ref="P17:V17"/>
+    <mergeCell ref="W5:AE5"/>
+    <mergeCell ref="D21:O21"/>
+    <mergeCell ref="W20:AE20"/>
+    <mergeCell ref="P19:V19"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D18:M18"/>
-    <mergeCell ref="Z22:AE22"/>
-    <mergeCell ref="T9:Y9"/>
-    <mergeCell ref="D8:M8"/>
-    <mergeCell ref="Z12:AE12"/>
-    <mergeCell ref="T11:Y11"/>
-    <mergeCell ref="Z5:AE5"/>
-    <mergeCell ref="Z14:AE14"/>
-    <mergeCell ref="N13:S13"/>
-    <mergeCell ref="D20:M20"/>
+    <mergeCell ref="W22:AE22"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="D16:O16"/>
+    <mergeCell ref="W12:AE12"/>
+    <mergeCell ref="P5:V5"/>
+    <mergeCell ref="W21:AE21"/>
+    <mergeCell ref="D18:O18"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="Z4:AE4"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="D22:M22"/>
+    <mergeCell ref="D8:O8"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="P21:V21"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:M13"/>
-    <mergeCell ref="T15:Y15"/>
-    <mergeCell ref="T24:Y24"/>
+    <mergeCell ref="P8:V8"/>
+    <mergeCell ref="D20:O20"/>
+    <mergeCell ref="W10:AE10"/>
     <mergeCell ref="B27:AE56"/>
-    <mergeCell ref="N7:S7"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="P23:V23"/>
+    <mergeCell ref="D22:O22"/>
+    <mergeCell ref="P7:V7"/>
+    <mergeCell ref="P16:V16"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="Z16:AE16"/>
-    <mergeCell ref="T10:Y10"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="Z18:AE18"/>
-    <mergeCell ref="D15:M15"/>
-    <mergeCell ref="N17:S17"/>
-    <mergeCell ref="D24:M24"/>
-    <mergeCell ref="Z8:AE8"/>
-    <mergeCell ref="Z17:AE17"/>
+    <mergeCell ref="D6:O6"/>
+    <mergeCell ref="D13:O13"/>
+    <mergeCell ref="P18:V18"/>
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="N19:S19"/>
-    <mergeCell ref="T17:Y17"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="T22:Y22"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="D10:M10"/>
+    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="W9:AE9"/>
+    <mergeCell ref="P20:V20"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="Z20:AE20"/>
-    <mergeCell ref="D19:M19"/>
-    <mergeCell ref="T6:Y6"/>
-    <mergeCell ref="T19:Y19"/>
+    <mergeCell ref="D24:O24"/>
+    <mergeCell ref="W23:AE23"/>
+    <mergeCell ref="P22:V22"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="Z6:AE6"/>
-    <mergeCell ref="D11:M11"/>
+    <mergeCell ref="W13:AE13"/>
+    <mergeCell ref="P6:V6"/>
+    <mergeCell ref="W4:AE4"/>
     <mergeCell ref="B26:AE26"/>
-    <mergeCell ref="T5:Y5"/>
-    <mergeCell ref="T20:Y20"/>
-    <mergeCell ref="T14:Y14"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="D19:O19"/>
+    <mergeCell ref="W15:AE15"/>
+    <mergeCell ref="W24:AE24"/>
     <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="T4:Y4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5948,182 +5423,36 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="9" t="n"/>
-      <c r="S22" s="9" t="n"/>
-      <c r="T22" s="9" t="n"/>
-      <c r="U22" s="9" t="n"/>
-      <c r="V22" s="9" t="n"/>
-      <c r="W22" s="9" t="n"/>
-      <c r="X22" s="9" t="n"/>
-      <c r="Y22" s="9" t="n"/>
-      <c r="Z22" s="9" t="n"/>
-      <c r="AA22" s="9" t="n"/>
-      <c r="AB22" s="9" t="n"/>
-      <c r="AC22" s="9" t="n"/>
-      <c r="AD22" s="9" t="n"/>
-      <c r="AE22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="11" t="n"/>
-      <c r="AE23" s="12" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="11" t="n"/>
-      <c r="AE24" s="12" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="11" t="n"/>
-      <c r="AE25" s="12" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="11" t="n"/>
-      <c r="AE26" s="12" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="11" t="n"/>
-      <c r="AE27" s="12" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="11" t="n"/>
-      <c r="AE28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="11" t="n"/>
-      <c r="AE29" s="12" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="11" t="n"/>
-      <c r="AE30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="11" t="n"/>
-      <c r="AE31" s="12" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="11" t="n"/>
-      <c r="AE32" s="12" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="11" t="n"/>
-      <c r="AE33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="B34" s="11" t="n"/>
-      <c r="AE34" s="12" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="11" t="n"/>
-      <c r="AE35" s="12" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="B36" s="11" t="n"/>
-      <c r="AE36" s="12" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="11" t="n"/>
-      <c r="AE37" s="12" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="11" t="n"/>
-      <c r="AE38" s="12" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="11" t="n"/>
-      <c r="AE39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="11" t="n"/>
-      <c r="AE40" s="12" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="B41" s="11" t="n"/>
-      <c r="AE41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="B42" s="11" t="n"/>
-      <c r="AE42" s="12" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="n"/>
-      <c r="AE43" s="12" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="11" t="n"/>
-      <c r="AE44" s="12" t="n"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="B45" s="11" t="n"/>
-      <c r="AE45" s="12" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="B46" s="11" t="n"/>
-      <c r="AE46" s="12" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="11" t="n"/>
-      <c r="AE47" s="12" t="n"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="B48" s="11" t="n"/>
-      <c r="AE48" s="12" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="11" t="n"/>
-      <c r="AE49" s="12" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="11" t="n"/>
-      <c r="AE50" s="12" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="14" t="n"/>
-      <c r="H51" s="14" t="n"/>
-      <c r="I51" s="14" t="n"/>
-      <c r="J51" s="14" t="n"/>
-      <c r="K51" s="14" t="n"/>
-      <c r="L51" s="14" t="n"/>
-      <c r="M51" s="14" t="n"/>
-      <c r="N51" s="14" t="n"/>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="14" t="n"/>
-      <c r="Q51" s="14" t="n"/>
-      <c r="R51" s="14" t="n"/>
-      <c r="S51" s="14" t="n"/>
-      <c r="T51" s="14" t="n"/>
-      <c r="U51" s="14" t="n"/>
-      <c r="V51" s="14" t="n"/>
-      <c r="W51" s="14" t="n"/>
-      <c r="X51" s="14" t="n"/>
-      <c r="Y51" s="14" t="n"/>
-      <c r="Z51" s="14" t="n"/>
-      <c r="AA51" s="14" t="n"/>
-      <c r="AB51" s="14" t="n"/>
-      <c r="AC51" s="14" t="n"/>
-      <c r="AD51" s="14" t="n"/>
-      <c r="AE51" s="15" t="n"/>
-    </row>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="20" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1"/>
     <row r="52" ht="8" customHeight="1"/>
   </sheetData>
   <mergeCells count="68">

--- a/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
@@ -1921,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AE66"/>
+  <dimension ref="B1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2024,1166 +2024,15 @@
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="4" t="n"/>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="3" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="n"/>
-      <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="3" t="n"/>
-      <c r="AC5" s="3" t="n"/>
-      <c r="AD5" s="3" t="n"/>
-      <c r="AE5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="4" t="n"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="3" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="5" t="inlineStr"/>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" s="3" t="n"/>
-      <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="3" t="n"/>
-      <c r="AC6" s="3" t="n"/>
-      <c r="AD6" s="3" t="n"/>
-      <c r="AE6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" s="4" t="n"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="5" t="inlineStr"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
-      <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="3" t="n"/>
-      <c r="AC7" s="3" t="n"/>
-      <c r="AD7" s="3" t="n"/>
-      <c r="AE7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" s="4" t="n"/>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="3" t="n"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="5" t="inlineStr"/>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
-      <c r="AA8" s="3" t="n"/>
-      <c r="AB8" s="3" t="n"/>
-      <c r="AC8" s="3" t="n"/>
-      <c r="AD8" s="3" t="n"/>
-      <c r="AE8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="4" t="n"/>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="5" t="inlineStr"/>
-      <c r="Y9" s="3" t="n"/>
-      <c r="Z9" s="3" t="n"/>
-      <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="3" t="n"/>
-      <c r="AC9" s="3" t="n"/>
-      <c r="AD9" s="3" t="n"/>
-      <c r="AE9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="4" t="n"/>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="5" t="inlineStr"/>
-      <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
-      <c r="AC10" s="3" t="n"/>
-      <c r="AD10" s="3" t="n"/>
-      <c r="AE10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" s="4" t="n"/>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="4" t="n"/>
-      <c r="X11" s="5" t="inlineStr"/>
-      <c r="Y11" s="3" t="n"/>
-      <c r="Z11" s="3" t="n"/>
-      <c r="AA11" s="3" t="n"/>
-      <c r="AB11" s="3" t="n"/>
-      <c r="AC11" s="3" t="n"/>
-      <c r="AD11" s="3" t="n"/>
-      <c r="AE11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="5" t="inlineStr"/>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
-      <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="4" t="n"/>
-      <c r="U12" s="5" t="inlineStr"/>
-      <c r="V12" s="3" t="n"/>
-      <c r="W12" s="4" t="n"/>
-      <c r="X12" s="5" t="inlineStr"/>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="n"/>
-      <c r="AA12" s="3" t="n"/>
-      <c r="AB12" s="3" t="n"/>
-      <c r="AC12" s="3" t="n"/>
-      <c r="AD12" s="3" t="n"/>
-      <c r="AE12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" s="4" t="n"/>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="5" t="inlineStr"/>
-      <c r="Y13" s="3" t="n"/>
-      <c r="Z13" s="3" t="n"/>
-      <c r="AA13" s="3" t="n"/>
-      <c r="AB13" s="3" t="n"/>
-      <c r="AC13" s="3" t="n"/>
-      <c r="AD13" s="3" t="n"/>
-      <c r="AE13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="4" t="n"/>
-      <c r="U14" s="5" t="inlineStr"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="4" t="n"/>
-      <c r="X14" s="5" t="inlineStr"/>
-      <c r="Y14" s="3" t="n"/>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
-      <c r="AC14" s="3" t="n"/>
-      <c r="AD14" s="3" t="n"/>
-      <c r="AE14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="5" t="inlineStr"/>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="4" t="n"/>
-      <c r="U15" s="5" t="inlineStr"/>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="5" t="inlineStr"/>
-      <c r="Y15" s="3" t="n"/>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
-      <c r="AC15" s="3" t="n"/>
-      <c r="AD15" s="3" t="n"/>
-      <c r="AE15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="4" t="n"/>
-      <c r="U16" s="5" t="inlineStr"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="5" t="inlineStr"/>
-      <c r="Y16" s="3" t="n"/>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
-      <c r="AC16" s="3" t="n"/>
-      <c r="AD16" s="3" t="n"/>
-      <c r="AE16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="5" t="inlineStr"/>
-      <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="4" t="n"/>
-      <c r="U17" s="5" t="inlineStr"/>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="5" t="inlineStr"/>
-      <c r="Y17" s="3" t="n"/>
-      <c r="Z17" s="3" t="n"/>
-      <c r="AA17" s="3" t="n"/>
-      <c r="AB17" s="3" t="n"/>
-      <c r="AC17" s="3" t="n"/>
-      <c r="AD17" s="3" t="n"/>
-      <c r="AE17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="5" t="inlineStr"/>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
-      <c r="R18" s="3" t="n"/>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="4" t="n"/>
-      <c r="U18" s="5" t="inlineStr"/>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="5" t="inlineStr"/>
-      <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
-      <c r="AA18" s="3" t="n"/>
-      <c r="AB18" s="3" t="n"/>
-      <c r="AC18" s="3" t="n"/>
-      <c r="AD18" s="3" t="n"/>
-      <c r="AE18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="5" t="inlineStr"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="4" t="n"/>
-      <c r="U19" s="5" t="inlineStr"/>
-      <c r="V19" s="3" t="n"/>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="5" t="inlineStr"/>
-      <c r="Y19" s="3" t="n"/>
-      <c r="Z19" s="3" t="n"/>
-      <c r="AA19" s="3" t="n"/>
-      <c r="AB19" s="3" t="n"/>
-      <c r="AC19" s="3" t="n"/>
-      <c r="AD19" s="3" t="n"/>
-      <c r="AE19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="5" t="inlineStr"/>
-      <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="4" t="n"/>
-      <c r="U20" s="5" t="inlineStr"/>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="5" t="inlineStr"/>
-      <c r="Y20" s="3" t="n"/>
-      <c r="Z20" s="3" t="n"/>
-      <c r="AA20" s="3" t="n"/>
-      <c r="AB20" s="3" t="n"/>
-      <c r="AC20" s="3" t="n"/>
-      <c r="AD20" s="3" t="n"/>
-      <c r="AE20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" s="4" t="n"/>
-      <c r="U21" s="5" t="inlineStr"/>
-      <c r="V21" s="3" t="n"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="5" t="inlineStr"/>
-      <c r="Y21" s="3" t="n"/>
-      <c r="Z21" s="3" t="n"/>
-      <c r="AA21" s="3" t="n"/>
-      <c r="AB21" s="3" t="n"/>
-      <c r="AC21" s="3" t="n"/>
-      <c r="AD21" s="3" t="n"/>
-      <c r="AE21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="3" t="n"/>
-      <c r="S22" s="3" t="n"/>
-      <c r="T22" s="4" t="n"/>
-      <c r="U22" s="5" t="inlineStr"/>
-      <c r="V22" s="3" t="n"/>
-      <c r="W22" s="4" t="n"/>
-      <c r="X22" s="5" t="inlineStr"/>
-      <c r="Y22" s="3" t="n"/>
-      <c r="Z22" s="3" t="n"/>
-      <c r="AA22" s="3" t="n"/>
-      <c r="AB22" s="3" t="n"/>
-      <c r="AC22" s="3" t="n"/>
-      <c r="AD22" s="3" t="n"/>
-      <c r="AE22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="4" t="n"/>
-      <c r="U23" s="5" t="inlineStr"/>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="4" t="n"/>
-      <c r="X23" s="5" t="inlineStr"/>
-      <c r="Y23" s="3" t="n"/>
-      <c r="Z23" s="3" t="n"/>
-      <c r="AA23" s="3" t="n"/>
-      <c r="AB23" s="3" t="n"/>
-      <c r="AC23" s="3" t="n"/>
-      <c r="AD23" s="3" t="n"/>
-      <c r="AE23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="n"/>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" s="4" t="n"/>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="3" t="n"/>
-      <c r="W24" s="4" t="n"/>
-      <c r="X24" s="5" t="inlineStr"/>
-      <c r="Y24" s="3" t="n"/>
-      <c r="Z24" s="3" t="n"/>
-      <c r="AA24" s="3" t="n"/>
-      <c r="AB24" s="3" t="n"/>
-      <c r="AC24" s="3" t="n"/>
-      <c r="AD24" s="3" t="n"/>
-      <c r="AE24" s="4" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="4" t="n"/>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="4" t="n"/>
-      <c r="X25" s="5" t="inlineStr"/>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
-      <c r="AC25" s="3" t="n"/>
-      <c r="AD25" s="3" t="n"/>
-      <c r="AE25" s="4" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="4" t="n"/>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="3" t="n"/>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="4" t="n"/>
-      <c r="U26" s="5" t="inlineStr"/>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="4" t="n"/>
-      <c r="X26" s="5" t="inlineStr"/>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
-      <c r="AC26" s="3" t="n"/>
-      <c r="AD26" s="3" t="n"/>
-      <c r="AE26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="3" t="n"/>
-      <c r="R27" s="3" t="n"/>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="4" t="n"/>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="4" t="n"/>
-      <c r="X27" s="5" t="inlineStr"/>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" s="3" t="n"/>
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" s="3" t="n"/>
-      <c r="AC27" s="3" t="n"/>
-      <c r="AD27" s="3" t="n"/>
-      <c r="AE27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="4" t="n"/>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="3" t="n"/>
-      <c r="Q28" s="3" t="n"/>
-      <c r="R28" s="3" t="n"/>
-      <c r="S28" s="3" t="n"/>
-      <c r="T28" s="4" t="n"/>
-      <c r="U28" s="5" t="inlineStr"/>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="4" t="n"/>
-      <c r="X28" s="5" t="inlineStr"/>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
-      <c r="AA28" s="3" t="n"/>
-      <c r="AB28" s="3" t="n"/>
-      <c r="AC28" s="3" t="n"/>
-      <c r="AD28" s="3" t="n"/>
-      <c r="AE28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="4" t="n"/>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="3" t="n"/>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" s="4" t="n"/>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="4" t="n"/>
-      <c r="X29" s="5" t="inlineStr"/>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" s="3" t="n"/>
-      <c r="AA29" s="3" t="n"/>
-      <c r="AB29" s="3" t="n"/>
-      <c r="AC29" s="3" t="n"/>
-      <c r="AD29" s="3" t="n"/>
-      <c r="AE29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="5" t="inlineStr"/>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="4" t="n"/>
-      <c r="U30" s="5" t="inlineStr"/>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="4" t="n"/>
-      <c r="X30" s="5" t="inlineStr"/>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
-      <c r="AA30" s="3" t="n"/>
-      <c r="AB30" s="3" t="n"/>
-      <c r="AC30" s="3" t="n"/>
-      <c r="AD30" s="3" t="n"/>
-      <c r="AE30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="n"/>
-      <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="4" t="n"/>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="4" t="n"/>
-      <c r="X31" s="5" t="inlineStr"/>
-      <c r="Y31" s="3" t="n"/>
-      <c r="Z31" s="3" t="n"/>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" s="3" t="n"/>
-      <c r="AC31" s="3" t="n"/>
-      <c r="AD31" s="3" t="n"/>
-      <c r="AE31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="4" t="n"/>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="4" t="n"/>
-      <c r="X32" s="5" t="inlineStr"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="n"/>
-      <c r="AA32" s="3" t="n"/>
-      <c r="AB32" s="3" t="n"/>
-      <c r="AC32" s="3" t="n"/>
-      <c r="AD32" s="3" t="n"/>
-      <c r="AE32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="5" t="inlineStr"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="4" t="n"/>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="3" t="n"/>
-      <c r="Q33" s="3" t="n"/>
-      <c r="R33" s="3" t="n"/>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="4" t="n"/>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="4" t="n"/>
-      <c r="X33" s="5" t="inlineStr"/>
-      <c r="Y33" s="3" t="n"/>
-      <c r="Z33" s="3" t="n"/>
-      <c r="AA33" s="3" t="n"/>
-      <c r="AB33" s="3" t="n"/>
-      <c r="AC33" s="3" t="n"/>
-      <c r="AD33" s="3" t="n"/>
-      <c r="AE33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="4" t="n"/>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="3" t="n"/>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="4" t="n"/>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="3" t="n"/>
-      <c r="W34" s="4" t="n"/>
-      <c r="X34" s="5" t="inlineStr"/>
-      <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
-      <c r="AA34" s="3" t="n"/>
-      <c r="AB34" s="3" t="n"/>
-      <c r="AC34" s="3" t="n"/>
-      <c r="AD34" s="3" t="n"/>
-      <c r="AE34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="26" customHeight="1">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>■ 2. オブジェクト関連図（自動生成）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1"/>
-    <row r="38" ht="20" customHeight="1"/>
-    <row r="39" ht="20" customHeight="1"/>
-    <row r="40" ht="20" customHeight="1"/>
-    <row r="41" ht="20" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1"/>
-    <row r="44" ht="20" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1"/>
-    <row r="47" ht="20" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1"/>
-    <row r="50" ht="20" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1"/>
-    <row r="53" ht="20" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1"/>
-    <row r="55" ht="20" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1"/>
-    <row r="57" ht="20" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1"/>
-    <row r="59" ht="20" customHeight="1"/>
-    <row r="60" ht="20" customHeight="1"/>
-    <row r="61" ht="20" customHeight="1"/>
-    <row r="62" ht="20" customHeight="1"/>
-    <row r="63" ht="20" customHeight="1"/>
-    <row r="64" ht="20" customHeight="1"/>
-    <row r="65" ht="20" customHeight="1"/>
-    <row r="66" ht="20" customHeight="1"/>
-    <row r="67" ht="8" customHeight="1"/>
   </sheetData>
-  <mergeCells count="159">
-    <mergeCell ref="X12:AE12"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="X21:AE21"/>
-    <mergeCell ref="U32:W32"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="X23:AE23"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="X13:AE13"/>
-    <mergeCell ref="X7:AE7"/>
-    <mergeCell ref="U18:W18"/>
-    <mergeCell ref="O12:T12"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="O14:T14"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="O23:T23"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="X33:AE33"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O13:T13"/>
-    <mergeCell ref="O7:T7"/>
-    <mergeCell ref="U34:W34"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="O15:T15"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="X25:AE25"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="X9:AE9"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X27:AE27"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="X11:AE11"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="O25:T25"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="U21:W21"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O27:T27"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="O11:T11"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="X6:AE6"/>
-    <mergeCell ref="X15:AE15"/>
-    <mergeCell ref="X24:AE24"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="U26:W26"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="X26:AE26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="X10:AE10"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="U25:W25"/>
-    <mergeCell ref="O32:T32"/>
-    <mergeCell ref="O26:T26"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="X17:AE17"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U28:W28"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="X19:AE19"/>
-    <mergeCell ref="X34:AE34"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="X28:AE28"/>
-    <mergeCell ref="O8:T8"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="U14:W14"/>
+  <mergeCells count="7">
+    <mergeCell ref="B1:AE1"/>
+    <mergeCell ref="X4:AE4"/>
     <mergeCell ref="H4:N4"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="U23:W23"/>
-    <mergeCell ref="X30:AE30"/>
+    <mergeCell ref="O4:T4"/>
     <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="X20:AE20"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="X14:AE14"/>
-    <mergeCell ref="U22:W22"/>
-    <mergeCell ref="X29:AE29"/>
-    <mergeCell ref="U31:W31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B36:AE36"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="O34:T34"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="X4:AE4"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="O28:T28"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="O9:T9"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="O30:T30"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="O29:T29"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="O22:T22"/>
-    <mergeCell ref="X32:AE32"/>
-    <mergeCell ref="O31:T31"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="X8:AE8"/>
-    <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="O21:T21"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="X16:AE16"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="B37:AE66"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="X18:AE18"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="U5:W5"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="B3:AE3"/>
     <mergeCell ref="B4:G4"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="O10:T10"/>
-    <mergeCell ref="O24:T24"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="O33:T33"/>
-    <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="X22:AE22"/>
-    <mergeCell ref="X31:AE31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
@@ -10,8 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改版履歴" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業務フロー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対象オブジェクト" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理概要" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理概要" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対象オブジェクト" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="関連コンポーネント" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -1960,7 +1960,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>詳細設計書 — 対象オブジェクト</t>
+          <t>詳細設計書 — 処理概要</t>
         </is>
       </c>
     </row>
@@ -1968,54 +1968,50 @@
     <row r="3" ht="26" customHeight="1">
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>■ 1. 対象オブジェクト・項目一覧</t>
+          <t>■ 1. 処理概要</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>オブジェクト名</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>項目API名</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>項目ラベル</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>コンポーネント</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
-      <c r="T4" s="4" t="n"/>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>読み書き区分</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>分岐条件</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="n"/>
@@ -2025,14 +2021,13 @@
       <c r="AE4" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="X4:AE4"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="P4:V4"/>
+    <mergeCell ref="D4:O4"/>
     <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="W4:AE4"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2083,7 +2078,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>詳細設計書 — 処理概要</t>
+          <t>詳細設計書 — 対象オブジェクト</t>
         </is>
       </c>
     </row>
@@ -2091,50 +2086,54 @@
     <row r="3" ht="26" customHeight="1">
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>■ 1. 処理概要</t>
+          <t>■ 1. 対象オブジェクト・項目一覧</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>処理内容</t>
-        </is>
-      </c>
+          <t>オブジェクト名</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>項目API名</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>コンポーネント</t>
-        </is>
-      </c>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>項目ラベル</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>分岐条件</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>読み書き区分</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="4" t="n"/>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="n"/>
@@ -2144,13 +2143,14 @@
       <c r="AE4" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="P4:V4"/>
-    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="X4:AE4"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="U4:W4"/>
     <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="W4:AE4"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2248,12 +2248,8 @@
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="6" t="inlineStr">
-        <is>
-          <t>依存方向</t>
-        </is>
-      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="n"/>
       <c r="AB4" s="3" t="n"/>
@@ -2262,10 +2258,9 @@
       <c r="AE4" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="N4:X4"/>
-    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="N4:AE4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="B3:AE3"/>
     <mergeCell ref="B4:I4"/>

--- a/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
@@ -683,12 +683,8 @@
         </is>
       </c>
       <c r="AB5" s="3" t="n"/>
-      <c r="AC5" s="4" t="n"/>
-      <c r="AD5" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="AC5" s="3" t="n"/>
+      <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="4" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -719,8 +715,8 @@
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="5" t="inlineStr"/>
       <c r="AB6" s="3" t="n"/>
-      <c r="AC6" s="4" t="n"/>
-      <c r="AD6" s="5" t="inlineStr"/>
+      <c r="AC6" s="3" t="n"/>
+      <c r="AD6" s="3" t="n"/>
       <c r="AE6" s="4" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -751,8 +747,8 @@
       <c r="Z7" s="4" t="n"/>
       <c r="AA7" s="5" t="inlineStr"/>
       <c r="AB7" s="3" t="n"/>
-      <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="5" t="inlineStr"/>
+      <c r="AC7" s="3" t="n"/>
+      <c r="AD7" s="3" t="n"/>
       <c r="AE7" s="4" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -783,8 +779,8 @@
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="5" t="inlineStr"/>
       <c r="AB8" s="3" t="n"/>
-      <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="5" t="inlineStr"/>
+      <c r="AC8" s="3" t="n"/>
+      <c r="AD8" s="3" t="n"/>
       <c r="AE8" s="4" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -815,8 +811,8 @@
       <c r="Z9" s="4" t="n"/>
       <c r="AA9" s="5" t="inlineStr"/>
       <c r="AB9" s="3" t="n"/>
-      <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="5" t="inlineStr"/>
+      <c r="AC9" s="3" t="n"/>
+      <c r="AD9" s="3" t="n"/>
       <c r="AE9" s="4" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -847,8 +843,8 @@
       <c r="Z10" s="4" t="n"/>
       <c r="AA10" s="5" t="inlineStr"/>
       <c r="AB10" s="3" t="n"/>
-      <c r="AC10" s="4" t="n"/>
-      <c r="AD10" s="5" t="inlineStr"/>
+      <c r="AC10" s="3" t="n"/>
+      <c r="AD10" s="3" t="n"/>
       <c r="AE10" s="4" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -879,8 +875,8 @@
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="5" t="inlineStr"/>
       <c r="AB11" s="3" t="n"/>
-      <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="5" t="inlineStr"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
       <c r="AE11" s="4" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -911,8 +907,8 @@
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="5" t="inlineStr"/>
       <c r="AB12" s="3" t="n"/>
-      <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="5" t="inlineStr"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
       <c r="AE12" s="4" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -943,8 +939,8 @@
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="5" t="inlineStr"/>
       <c r="AB13" s="3" t="n"/>
-      <c r="AC13" s="4" t="n"/>
-      <c r="AD13" s="5" t="inlineStr"/>
+      <c r="AC13" s="3" t="n"/>
+      <c r="AD13" s="3" t="n"/>
       <c r="AE13" s="4" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -975,8 +971,8 @@
       <c r="Z14" s="4" t="n"/>
       <c r="AA14" s="5" t="inlineStr"/>
       <c r="AB14" s="3" t="n"/>
-      <c r="AC14" s="4" t="n"/>
-      <c r="AD14" s="5" t="inlineStr"/>
+      <c r="AC14" s="3" t="n"/>
+      <c r="AD14" s="3" t="n"/>
       <c r="AE14" s="4" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1007,8 +1003,8 @@
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="5" t="inlineStr"/>
       <c r="AB15" s="3" t="n"/>
-      <c r="AC15" s="4" t="n"/>
-      <c r="AD15" s="5" t="inlineStr"/>
+      <c r="AC15" s="3" t="n"/>
+      <c r="AD15" s="3" t="n"/>
       <c r="AE15" s="4" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1039,8 +1035,8 @@
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="5" t="inlineStr"/>
       <c r="AB16" s="3" t="n"/>
-      <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="5" t="inlineStr"/>
+      <c r="AC16" s="3" t="n"/>
+      <c r="AD16" s="3" t="n"/>
       <c r="AE16" s="4" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1071,8 +1067,8 @@
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="5" t="inlineStr"/>
       <c r="AB17" s="3" t="n"/>
-      <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="5" t="inlineStr"/>
+      <c r="AC17" s="3" t="n"/>
+      <c r="AD17" s="3" t="n"/>
       <c r="AE17" s="4" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1103,8 +1099,8 @@
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="5" t="inlineStr"/>
       <c r="AB18" s="3" t="n"/>
-      <c r="AC18" s="4" t="n"/>
-      <c r="AD18" s="5" t="inlineStr"/>
+      <c r="AC18" s="3" t="n"/>
+      <c r="AD18" s="3" t="n"/>
       <c r="AE18" s="4" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1135,8 +1131,8 @@
       <c r="Z19" s="4" t="n"/>
       <c r="AA19" s="5" t="inlineStr"/>
       <c r="AB19" s="3" t="n"/>
-      <c r="AC19" s="4" t="n"/>
-      <c r="AD19" s="5" t="inlineStr"/>
+      <c r="AC19" s="3" t="n"/>
+      <c r="AD19" s="3" t="n"/>
       <c r="AE19" s="4" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1167,8 +1163,8 @@
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="5" t="inlineStr"/>
       <c r="AB20" s="3" t="n"/>
-      <c r="AC20" s="4" t="n"/>
-      <c r="AD20" s="5" t="inlineStr"/>
+      <c r="AC20" s="3" t="n"/>
+      <c r="AD20" s="3" t="n"/>
       <c r="AE20" s="4" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1199,8 +1195,8 @@
       <c r="Z21" s="4" t="n"/>
       <c r="AA21" s="5" t="inlineStr"/>
       <c r="AB21" s="3" t="n"/>
-      <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="5" t="inlineStr"/>
+      <c r="AC21" s="3" t="n"/>
+      <c r="AD21" s="3" t="n"/>
       <c r="AE21" s="4" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1231,8 +1227,8 @@
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="5" t="inlineStr"/>
       <c r="AB22" s="3" t="n"/>
-      <c r="AC22" s="4" t="n"/>
-      <c r="AD22" s="5" t="inlineStr"/>
+      <c r="AC22" s="3" t="n"/>
+      <c r="AD22" s="3" t="n"/>
       <c r="AE22" s="4" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1263,8 +1259,8 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="5" t="inlineStr"/>
       <c r="AB23" s="3" t="n"/>
-      <c r="AC23" s="4" t="n"/>
-      <c r="AD23" s="5" t="inlineStr"/>
+      <c r="AC23" s="3" t="n"/>
+      <c r="AD23" s="3" t="n"/>
       <c r="AE23" s="4" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1295,8 +1291,8 @@
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="5" t="inlineStr"/>
       <c r="AB24" s="3" t="n"/>
-      <c r="AC24" s="4" t="n"/>
-      <c r="AD24" s="5" t="inlineStr"/>
+      <c r="AC24" s="3" t="n"/>
+      <c r="AD24" s="3" t="n"/>
       <c r="AE24" s="4" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1327,36 +1323,33 @@
       <c r="Z25" s="4" t="n"/>
       <c r="AA25" s="5" t="inlineStr"/>
       <c r="AB25" s="3" t="n"/>
-      <c r="AC25" s="4" t="n"/>
-      <c r="AD25" s="5" t="inlineStr"/>
+      <c r="AC25" s="3" t="n"/>
+      <c r="AD25" s="3" t="n"/>
       <c r="AE25" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="173">
+  <mergeCells count="152">
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="AA5:AC5"/>
-    <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="AA22:AE22"/>
+    <mergeCell ref="R24:W24"/>
     <mergeCell ref="L15:Q15"/>
-    <mergeCell ref="R24:W24"/>
     <mergeCell ref="X18:Z18"/>
     <mergeCell ref="L18:Q18"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="D22:E22"/>
     <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="D22:E22"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="X5:Z5"/>
     <mergeCell ref="L10:Q10"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AA6:AE6"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="X22:Z22"/>
-    <mergeCell ref="AA8:AC8"/>
     <mergeCell ref="X12:Z12"/>
     <mergeCell ref="F3:R3"/>
     <mergeCell ref="L17:Q17"/>
@@ -1364,145 +1357,127 @@
     <mergeCell ref="F11:K11"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="F25:K25"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="AA10:AC10"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="AD16:AE16"/>
     <mergeCell ref="L19:Q19"/>
     <mergeCell ref="X23:Z23"/>
     <mergeCell ref="R13:W13"/>
     <mergeCell ref="X13:Z13"/>
     <mergeCell ref="X7:Z7"/>
     <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="AA8:AE8"/>
     <mergeCell ref="F15:K15"/>
     <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="F24:K24"/>
+    <mergeCell ref="AA17:AE17"/>
     <mergeCell ref="R6:W6"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="F24:K24"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="AD8:AE8"/>
     <mergeCell ref="R15:W15"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="L5:Q5"/>
     <mergeCell ref="L14:Q14"/>
+    <mergeCell ref="AA10:AE10"/>
     <mergeCell ref="L23:Q23"/>
     <mergeCell ref="R12:W12"/>
-    <mergeCell ref="AA20:AC20"/>
+    <mergeCell ref="AA19:AE19"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="R21:W21"/>
+    <mergeCell ref="AA9:AE9"/>
     <mergeCell ref="F23:K23"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="F13:K13"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="AA12:AC12"/>
-    <mergeCell ref="AA21:AC21"/>
+    <mergeCell ref="AA5:AE5"/>
     <mergeCell ref="X25:Z25"/>
+    <mergeCell ref="AA20:AE20"/>
     <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AA14:AC14"/>
     <mergeCell ref="R18:W18"/>
-    <mergeCell ref="AA23:AC23"/>
     <mergeCell ref="R8:W8"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="X11:Z11"/>
     <mergeCell ref="L16:Q16"/>
-    <mergeCell ref="AD22:AE22"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="AA12:AE12"/>
     <mergeCell ref="F19:K19"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="F16:K16"/>
     <mergeCell ref="R10:W10"/>
     <mergeCell ref="F6:K6"/>
     <mergeCell ref="D15:E15"/>
+    <mergeCell ref="AA21:AE21"/>
     <mergeCell ref="R19:W19"/>
     <mergeCell ref="D23:E23"/>
+    <mergeCell ref="AA14:AE14"/>
+    <mergeCell ref="AA23:AE23"/>
     <mergeCell ref="R25:W25"/>
     <mergeCell ref="F5:K5"/>
     <mergeCell ref="F20:K20"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="AD24:AE24"/>
     <mergeCell ref="F17:K17"/>
     <mergeCell ref="X15:Z15"/>
     <mergeCell ref="L20:Q20"/>
     <mergeCell ref="X24:Z24"/>
-    <mergeCell ref="AA25:AC25"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="AA18:AC18"/>
-    <mergeCell ref="AD19:AE19"/>
+    <mergeCell ref="L22:Q22"/>
     <mergeCell ref="F9:K9"/>
-    <mergeCell ref="L22:Q22"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="L6:Q6"/>
     <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="AA11:AC11"/>
     <mergeCell ref="L21:Q21"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="AA25:AE25"/>
     <mergeCell ref="R23:W23"/>
-    <mergeCell ref="AD11:AE11"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="F10:K10"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="AA13:AC13"/>
+    <mergeCell ref="AA11:AE11"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="X17:Z17"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F7:K7"/>
-    <mergeCell ref="AA6:AC6"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AA15:AC15"/>
-    <mergeCell ref="AD9:AE9"/>
     <mergeCell ref="R16:W16"/>
     <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="AD21:AE21"/>
     <mergeCell ref="L24:Q24"/>
-    <mergeCell ref="AA24:AC24"/>
     <mergeCell ref="F18:K18"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AD14:AE14"/>
     <mergeCell ref="F8:K8"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AA13:AE13"/>
+    <mergeCell ref="R20:W20"/>
     <mergeCell ref="X6:Z6"/>
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="AA7:AC7"/>
-    <mergeCell ref="R20:W20"/>
-    <mergeCell ref="AA16:AC16"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="X20:Z20"/>
     <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="L25:Q25"/>
+    <mergeCell ref="AA15:AE15"/>
     <mergeCell ref="F22:K22"/>
     <mergeCell ref="R17:W17"/>
-    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="AA24:AE24"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="AD15:AE15"/>
+    <mergeCell ref="R22:W22"/>
     <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="R22:W22"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="L11:Q11"/>
+    <mergeCell ref="AA7:AE7"/>
     <mergeCell ref="F14:K14"/>
     <mergeCell ref="R9:W9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="R5:W5"/>
-    <mergeCell ref="AA17:AC17"/>
+    <mergeCell ref="AA16:AE16"/>
     <mergeCell ref="R14:W14"/>
-    <mergeCell ref="AA22:AC22"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="R11:W11"/>
-    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="AA18:AE18"/>
     <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="AA9:AC9"/>
     <mergeCell ref="L13:Q13"/>
     <mergeCell ref="F12:K12"/>
     <mergeCell ref="F21:K21"/>
@@ -2103,7 +2078,7 @@
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>項目API名</t>
+          <t>項目ラベル</t>
         </is>
       </c>
       <c r="I4" s="3" t="n"/>
@@ -2114,7 +2089,7 @@
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>項目ラベル</t>
+          <t>項目API名</t>
         </is>
       </c>
       <c r="P4" s="3" t="n"/>

--- a/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
@@ -1969,23 +1969,19 @@
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>コンポーネント</t>
-        </is>
-      </c>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>コンポーネント</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>分岐条件</t>
-        </is>
-      </c>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
@@ -1996,12 +1992,11 @@
       <c r="AE4" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="P4:V4"/>
-    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="D4:S4"/>
     <mergeCell ref="B3:AE3"/>
-    <mergeCell ref="W4:AE4"/>
+    <mergeCell ref="T4:AE4"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/詳細設計書テンプレート.xlsx
@@ -1862,12 +1862,8 @@
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>分岐条件</t>
-        </is>
-      </c>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
@@ -1878,12 +1874,11 @@
       <c r="AE4" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="I4:V4"/>
     <mergeCell ref="B3:AE3"/>
+    <mergeCell ref="I4:AE4"/>
     <mergeCell ref="D4:H4"/>
-    <mergeCell ref="W4:AE4"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
